--- a/business-libraries/test-data/student_case/attribution.xlsx
+++ b/business-libraries/test-data/student_case/attribution.xlsx
@@ -4,8 +4,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="⑤b 归因-计算变量" sheetId="1" r:id="rId1"/>
-    <sheet name="⑤c 归因-分级规则" sheetId="2" r:id="rId2"/>
-    <sheet name="⑥ 归因-红线熔断" sheetId="3" r:id="rId3"/>
+    <sheet name="⑤c 归因项" sheetId="2" r:id="rId2"/>
+    <sheet name="⑤d 证据规则" sheetId="3" r:id="rId3"/>
+    <sheet name="⑤e 分级规则" sheetId="4" r:id="rId4"/>
+    <sheet name="⑥ 归因-红线熔断" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -399,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -426,7 +428,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>总负荷指数</v>
+        <v>筛查总分</v>
       </c>
       <c r="B2" t="str">
         <v>student_case</v>
@@ -435,10 +437,10 @@
         <v>总分</v>
       </c>
       <c r="D2" t="str">
-        <v>五题得分总和</v>
+        <v>五类筛查总分</v>
       </c>
       <c r="E2" t="str">
-        <v>ST_FIVE_Q</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -447,367 +449,784 @@
         <v/>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>情绪耗竭指数</v>
-      </c>
-      <c r="B3" t="str">
-        <v>student_case</v>
-      </c>
-      <c r="C3" t="str">
-        <v>维度[EMOTION]</v>
-      </c>
-      <c r="D3" t="str">
-        <v>情绪状态维度均值</v>
-      </c>
-      <c r="E3" t="str">
-        <v>ST_FIVE_Q</v>
-      </c>
-      <c r="F3" t="str">
-        <v>q1</v>
-      </c>
-      <c r="G3" t="str">
-        <v>EMOTION</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>连续低意义感次数</v>
-      </c>
-      <c r="B4" t="str">
-        <v>student_case</v>
-      </c>
-      <c r="C4" t="str">
-        <v>COUNT_CONSECUTIVE(题[q3] &lt;= 2, 4)</v>
-      </c>
-      <c r="D4" t="str">
-        <v>统计最近连续4次评估中意义感知得分&lt;=2的次数</v>
-      </c>
-      <c r="E4" t="str">
-        <v>ST_FIVE_Q</v>
-      </c>
-      <c r="F4" t="str">
-        <v>q3</v>
-      </c>
-      <c r="G4" t="str">
-        <v>MEANING</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:J6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>规则编码*</v>
+        <v>归因编码*</v>
       </c>
       <c r="B1" t="str">
+        <v>归因名称*</v>
+      </c>
+      <c r="C1" t="str">
         <v>所属模块*</v>
       </c>
-      <c r="C1" t="str">
-        <v>依据量表编码*</v>
-      </c>
       <c r="D1" t="str">
-        <v>优先级*</v>
+        <v>权重基数*</v>
       </c>
       <c r="E1" t="str">
-        <v>触发条件</v>
+        <v>工具标签*</v>
       </c>
       <c r="F1" t="str">
-        <v>命中等级*</v>
+        <v>归因说明</v>
       </c>
       <c r="G1" t="str">
-        <v>等级中文名*</v>
+        <v>高分表现</v>
       </c>
       <c r="H1" t="str">
-        <v>是否红线熔断*</v>
+        <v>典型诱因</v>
       </c>
       <c r="I1" t="str">
-        <v>主归因*</v>
+        <v>建议动作</v>
       </c>
       <c r="J1" t="str">
-        <v>次归因</v>
-      </c>
-      <c r="K1" t="str">
-        <v>归因理由*</v>
-      </c>
-      <c r="L1" t="str">
-        <v>工具标签*</v>
-      </c>
-      <c r="M1" t="str">
-        <v>结果说明*</v>
-      </c>
-      <c r="N1" t="str">
-        <v>输出动作摘要</v>
-      </c>
-      <c r="O1" t="str">
-        <v>输出工具摘要</v>
-      </c>
-      <c r="P1" t="str">
-        <v>升级条件</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>升级目标</v>
-      </c>
-      <c r="R1" t="str">
-        <v>复评触发条件</v>
-      </c>
-      <c r="S1" t="str">
         <v>手册出处</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ST-RED-Q1-Q3</v>
+        <v>SC_AT_EMOTION</v>
       </c>
       <c r="B2" t="str">
+        <v>情绪调节困难</v>
+      </c>
+      <c r="C2" t="str">
         <v>student_case</v>
       </c>
-      <c r="C2" t="str">
-        <v>ST_FIVE_Q</v>
-      </c>
       <c r="D2" t="str">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="E2" t="str">
-        <v>题[q1] &gt;= 4 且 题[q3] &gt;= 4</v>
+        <v>student_case,emotion</v>
       </c>
       <c r="F2" t="str">
-        <v>red</v>
+        <v>学生持续出现低落、焦虑或退缩，且难以表达和调节当前感受。</v>
       </c>
       <c r="G2" t="str">
-        <v>需立即关注</v>
+        <v>持续低落或易怒；很难说清自己的感受</v>
       </c>
       <c r="H2" t="str">
-        <v>是</v>
+        <v>可能与家庭变化、同伴关系或学业压力相关</v>
       </c>
       <c r="I2" t="str">
-        <v>行为与情绪双重危机</v>
+        <v>本周做一次低压力谈话，从可观察事实开始，不贴标签</v>
       </c>
       <c r="J2" t="str">
-        <v>情绪耗竭</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Q1疲劳&gt;=4分且Q3意义感&lt;=2分，两者同时处于高危水平，教师可能正经历情绪耗竭的核心阶段</v>
-      </c>
-      <c r="L2" t="str">
-        <v>student_case,red,behavior</v>
-      </c>
-      <c r="M2" t="str">
-        <v>行为与情绪双重危机风险同时处于高位，已暂停常规建议并转介。</v>
-      </c>
-      <c r="N2" t="str">
-        <v>建议安排心理专员面谈，暂缓常规班级评估</v>
-      </c>
-      <c r="O2" t="str">
-        <v>行为契约模板（应急）、情绪温度计自评</v>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v/>
-      </c>
-      <c r="R2" t="str">
-        <v>下次评估Q1或Q3任一&gt;=3分时触发复评</v>
-      </c>
-      <c r="S2" t="str">
-        <v>PRD 8.2.1</v>
+        <v>学生个体问题手册v1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ST-ORANGE</v>
+        <v>SC_AT_BEHAVIOR</v>
       </c>
       <c r="B3" t="str">
+        <v>行为调控困难</v>
+      </c>
+      <c r="C3" t="str">
         <v>student_case</v>
       </c>
-      <c r="C3" t="str">
-        <v>ST_FIVE_Q</v>
-      </c>
       <c r="D3" t="str">
-        <v>20</v>
+        <v>1.3</v>
       </c>
       <c r="E3" t="str">
-        <v>总分 &gt;= 17</v>
+        <v>student_case,behavior</v>
       </c>
       <c r="F3" t="str">
-        <v>orange</v>
+        <v>冲动、对抗或规则破坏行为频繁出现，且诱因难以预测。</v>
       </c>
       <c r="G3" t="str">
-        <v>需关注</v>
+        <v>行为频繁且场景不可预测；已影响他人学习</v>
       </c>
       <c r="H3" t="str">
-        <v>否</v>
+        <v>可能与执行功能、情绪调节或环境刺激相关</v>
       </c>
       <c r="I3" t="str">
-        <v>学业动机严重低下</v>
+        <v>完成一周 ABC 结构化观察，记录行为前情境、行为本身和行为后结果</v>
       </c>
       <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v>总分&gt;=17分，教师在多个维度上感受到压力，但未达到红线阈值</v>
-      </c>
-      <c r="L3" t="str">
-        <v>student_case,orange,motivation</v>
-      </c>
-      <c r="M3" t="str">
-        <v>您的整体状态在多个维度上偏高，建议重点关注并选择1-2项工具开始调整。</v>
-      </c>
-      <c r="N3" t="str">
-        <v>建议本月内完成一次深度自评</v>
-      </c>
-      <c r="O3" t="str">
-        <v>动机激发方案、同伴支持计划</v>
-      </c>
-      <c r="P3" t="str">
-        <v>连续3次评估仍为orange</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>升级至red评估流程</v>
-      </c>
-      <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="S3" t="str">
-        <v>PRD 8.2.1</v>
+        <v>学生个体问题手册v1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ST-YELLOW</v>
+        <v>SC_AT_SOCIAL</v>
       </c>
       <c r="B4" t="str">
+        <v>同伴关系受损</v>
+      </c>
+      <c r="C4" t="str">
         <v>student_case</v>
       </c>
-      <c r="C4" t="str">
-        <v>ST_FIVE_Q</v>
-      </c>
       <c r="D4" t="str">
-        <v>30</v>
+        <v>1.2</v>
       </c>
       <c r="E4" t="str">
-        <v>维度[EMOTION] &gt;= 3.5</v>
+        <v>student_case,social</v>
       </c>
       <c r="F4" t="str">
-        <v>yellow</v>
+        <v>与同伴的冲突、排斥或孤立反复发生，缺少稳定的支持关系。</v>
       </c>
       <c r="G4" t="str">
-        <v>需留意</v>
+        <v>被孤立或反复冲突；常规修复方式无效</v>
       </c>
       <c r="H4" t="str">
-        <v>否</v>
+        <v>社交技能不足或班级关系结构问题</v>
       </c>
       <c r="I4" t="str">
-        <v>人际关系与自尊双低</v>
+        <v>安排一次结构化的同伴配对活动，并观察互动质量</v>
       </c>
       <c r="J4" t="str">
-        <v>情绪耗竭</v>
-      </c>
-      <c r="K4" t="str">
-        <v>情绪耗竭维度得分偏高，可能出现轻度职业倦怠的早期信号</v>
-      </c>
-      <c r="L4" t="str">
-        <v>student_case,yellow,peer</v>
-      </c>
-      <c r="M4" t="str">
-        <v>您的情绪耗竭维度偏高，建议开始关注自我照顾。</v>
-      </c>
-      <c r="N4" t="str">
-        <v>建议使用自我照顾工具</v>
-      </c>
-      <c r="O4" t="str">
-        <v>动机激发方案、同伴支持圈</v>
-      </c>
-      <c r="P4" t="str">
-        <v>连续2次评估仍为yellow</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>升级至orange评估流程</v>
-      </c>
-      <c r="R4" t="str">
-        <v/>
-      </c>
-      <c r="S4" t="str">
-        <v>PRD 8.2.1</v>
+        <v>学生个体问题手册v1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ST-GREEN</v>
+        <v>SC_AT_ACADEMIC</v>
       </c>
       <c r="B5" t="str">
+        <v>学业功能下降</v>
+      </c>
+      <c r="C5" t="str">
         <v>student_case</v>
       </c>
-      <c r="C5" t="str">
-        <v>ST_FIVE_Q</v>
-      </c>
       <c r="D5" t="str">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>student_case,academic</v>
       </c>
       <c r="F5" t="str">
-        <v>green</v>
+        <v>学业表现持续下降，且已有常规支持措施没有带来改善。</v>
       </c>
       <c r="G5" t="str">
-        <v>状态良好</v>
+        <v>成绩持续下滑；作业和听课明显受影响</v>
       </c>
       <c r="H5" t="str">
-        <v>否</v>
+        <v>可能是学习问题模块的信号，需要交叉评估</v>
       </c>
       <c r="I5" t="str">
-        <v>状态稳定</v>
+        <v>转入学习问题模块做三层诊断，区分行为、认知与关系层面的卡点</v>
       </c>
       <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v>当前评估未触发任何风险规则，教师整体状态稳定</v>
-      </c>
-      <c r="L5" t="str">
-        <v>student_case,green</v>
-      </c>
-      <c r="M5" t="str">
-        <v>当前状态整体稳定，保持现有节奏即可。</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v/>
-      </c>
-      <c r="Q5" t="str">
-        <v/>
-      </c>
-      <c r="R5" t="str">
-        <v/>
-      </c>
-      <c r="S5" t="str">
-        <v>PRD 8.2.1</v>
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>SC_AT_ADAPT</v>
+      </c>
+      <c r="B6" t="str">
+        <v>适应障碍信号</v>
+      </c>
+      <c r="C6" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="D6" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="E6" t="str">
+        <v>student_case,adapt,crisis</v>
+      </c>
+      <c r="F6" t="str">
+        <v>出现拒学、躯体化或明显回避，且持续四周以上没有改善趋势。</v>
+      </c>
+      <c r="G6" t="str">
+        <v>拒学、躯体不适、明显回避；持续四周以上</v>
+      </c>
+      <c r="H6" t="str">
+        <v>重大生活事件或长期压力累积</v>
+      </c>
+      <c r="I6" t="str">
+        <v>整理时间线与已尝试措施，启动专业会商流程</v>
+      </c>
+      <c r="J6" t="str">
+        <v>学生个体问题手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G16"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>证据编码*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>归因编码*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>依据量表编码*</v>
+      </c>
+      <c r="D1" t="str">
+        <v>触发条件*</v>
+      </c>
+      <c r="E1" t="str">
+        <v>证据权重*</v>
+      </c>
+      <c r="F1" t="str">
+        <v>证据说明*</v>
+      </c>
+      <c r="G1" t="str">
+        <v>手册出处</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SC_EV_01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>SC_AT_EMOTION</v>
+      </c>
+      <c r="C2" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="D2" t="str">
+        <v>维度[SC_EMOTION] &gt;= 4</v>
+      </c>
+      <c r="E2" t="str">
+        <v>3</v>
+      </c>
+      <c r="F2" t="str">
+        <v>情绪维度处于高位，已影响日常功能</v>
+      </c>
+      <c r="G2" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SC_EV_02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>SC_AT_EMOTION</v>
+      </c>
+      <c r="C3" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="D3" t="str">
+        <v>维度[SC_EMOTION] &gt;= 3</v>
+      </c>
+      <c r="E3" t="str">
+        <v>1</v>
+      </c>
+      <c r="F3" t="str">
+        <v>情绪维度出现需要关注的信号</v>
+      </c>
+      <c r="G3" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SC_EV_03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>SC_AT_BEHAVIOR</v>
+      </c>
+      <c r="C4" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="D4" t="str">
+        <v>维度[SC_BEHAVIOR] &gt;= 4</v>
+      </c>
+      <c r="E4" t="str">
+        <v>3</v>
+      </c>
+      <c r="F4" t="str">
+        <v>行为维度处于高位，行为频繁且难以预测</v>
+      </c>
+      <c r="G4" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>SC_EV_04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>SC_AT_BEHAVIOR</v>
+      </c>
+      <c r="C5" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="D5" t="str">
+        <v>维度[SC_BEHAVIOR] &gt;= 3</v>
+      </c>
+      <c r="E5" t="str">
+        <v>1</v>
+      </c>
+      <c r="F5" t="str">
+        <v>行为维度出现需要关注的信号</v>
+      </c>
+      <c r="G5" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>SC_EV_05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>SC_AT_SOCIAL</v>
+      </c>
+      <c r="C6" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="D6" t="str">
+        <v>维度[SC_SOCIAL] &gt;= 4</v>
+      </c>
+      <c r="E6" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F6" t="str">
+        <v>同伴社交维度处于高位，冲突或孤立反复发生</v>
+      </c>
+      <c r="G6" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>SC_EV_06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>SC_AT_SOCIAL</v>
+      </c>
+      <c r="C7" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="D7" t="str">
+        <v>维度[SC_SOCIAL] &gt;= 3</v>
+      </c>
+      <c r="E7" t="str">
+        <v>1</v>
+      </c>
+      <c r="F7" t="str">
+        <v>同伴社交出现需要关注的信号</v>
+      </c>
+      <c r="G7" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>SC_EV_07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>SC_AT_ACADEMIC</v>
+      </c>
+      <c r="C8" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="D8" t="str">
+        <v>维度[SC_ACADEMIC] &gt;= 4</v>
+      </c>
+      <c r="E8" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F8" t="str">
+        <v>学业维度处于高位且常规支持无效</v>
+      </c>
+      <c r="G8" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>SC_EV_08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>SC_AT_ACADEMIC</v>
+      </c>
+      <c r="C9" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="D9" t="str">
+        <v>维度[SC_ACADEMIC] &gt;= 3</v>
+      </c>
+      <c r="E9" t="str">
+        <v>1</v>
+      </c>
+      <c r="F9" t="str">
+        <v>学业表现出现下降</v>
+      </c>
+      <c r="G9" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SC_EV_09</v>
+      </c>
+      <c r="B10" t="str">
+        <v>SC_AT_ADAPT</v>
+      </c>
+      <c r="C10" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="D10" t="str">
+        <v>维度[SC_ADAPT] &gt;= 4</v>
+      </c>
+      <c r="E10" t="str">
+        <v>3.5</v>
+      </c>
+      <c r="F10" t="str">
+        <v>适应维度处于高位，出现拒学或躯体化信号</v>
+      </c>
+      <c r="G10" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SC_EV_10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>SC_AT_ADAPT</v>
+      </c>
+      <c r="C11" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="D11" t="str">
+        <v>题[adp3] &gt;= 4</v>
+      </c>
+      <c r="E11" t="str">
+        <v>2</v>
+      </c>
+      <c r="F11" t="str">
+        <v>问题已持续四周以上且无改善趋势</v>
+      </c>
+      <c r="G11" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>SC_EV_11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>SC_AT_ADAPT</v>
+      </c>
+      <c r="C12" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="D12" t="str">
+        <v>维度[SC_ADAPT] &gt;= 3</v>
+      </c>
+      <c r="E12" t="str">
+        <v>1</v>
+      </c>
+      <c r="F12" t="str">
+        <v>适应状况出现需要关注的信号</v>
+      </c>
+      <c r="G12" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>SC_EV_21</v>
+      </c>
+      <c r="B13" t="str">
+        <v>SC_AT_BEHAVIOR</v>
+      </c>
+      <c r="C13" t="str">
+        <v>SC_EBRCA</v>
+      </c>
+      <c r="D13" t="str">
+        <v>维度[SC_TRIGGER] &gt;= 3.5</v>
+      </c>
+      <c r="E13" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F13" t="str">
+        <v>结构化观察显示行为诱因不清晰，难以预防</v>
+      </c>
+      <c r="G13" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>SC_EV_22</v>
+      </c>
+      <c r="B14" t="str">
+        <v>SC_AT_ADAPT</v>
+      </c>
+      <c r="C14" t="str">
+        <v>SC_EBRCA</v>
+      </c>
+      <c r="D14" t="str">
+        <v>维度[SC_FUNCTION] &gt;= 3.5</v>
+      </c>
+      <c r="E14" t="str">
+        <v>3</v>
+      </c>
+      <c r="F14" t="str">
+        <v>结构化观察显示功能影响已经明显</v>
+      </c>
+      <c r="G14" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>SC_EV_23</v>
+      </c>
+      <c r="B15" t="str">
+        <v>SC_AT_EMOTION</v>
+      </c>
+      <c r="C15" t="str">
+        <v>SC_EBRCA</v>
+      </c>
+      <c r="D15" t="str">
+        <v>维度[SC_SUPPORT_TRIED] &gt;= 3.5</v>
+      </c>
+      <c r="E15" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F15" t="str">
+        <v>已尝试的支持措施基本无效，需要升级支持层级</v>
+      </c>
+      <c r="G15" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>SC_EV_24</v>
+      </c>
+      <c r="B16" t="str">
+        <v>SC_AT_SOCIAL</v>
+      </c>
+      <c r="C16" t="str">
+        <v>SC_EBRCA</v>
+      </c>
+      <c r="D16" t="str">
+        <v>维度[SC_FUNCTION] &gt;= 3</v>
+      </c>
+      <c r="E16" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F16" t="str">
+        <v>功能影响已波及正常互动</v>
+      </c>
+      <c r="G16" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>规则编码*</v>
+      </c>
+      <c r="B1" t="str">
+        <v>所属模块*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>依据量表编码</v>
+      </c>
+      <c r="D1" t="str">
+        <v>优先级*</v>
+      </c>
+      <c r="E1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="F1" t="str">
+        <v>命中等级*</v>
+      </c>
+      <c r="G1" t="str">
+        <v>等级中文名*</v>
+      </c>
+      <c r="H1" t="str">
+        <v>严重度*</v>
+      </c>
+      <c r="I1" t="str">
+        <v>是否红线熔断*</v>
+      </c>
+      <c r="J1" t="str">
+        <v>结果说明*</v>
+      </c>
+      <c r="K1" t="str">
+        <v>升级条件</v>
+      </c>
+      <c r="L1" t="str">
+        <v>升级目标</v>
+      </c>
+      <c r="M1" t="str">
+        <v>复评触发条件</v>
+      </c>
+      <c r="N1" t="str">
+        <v>手册出处</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SC_GRADE_L3</v>
+      </c>
+      <c r="B2" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="C2" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="D2" t="str">
+        <v>10</v>
+      </c>
+      <c r="E2" t="str">
+        <v>筛查总分 &gt;= 52</v>
+      </c>
+      <c r="F2" t="str">
+        <v>L3</v>
+      </c>
+      <c r="G2" t="str">
+        <v>L3 专业会商</v>
+      </c>
+      <c r="H2" t="str">
+        <v>crisis</v>
+      </c>
+      <c r="I2" t="str">
+        <v>是</v>
+      </c>
+      <c r="J2" t="str">
+        <v>多个维度同时处于高位，已达到专业会商层级，请整理材料并启动转介。</v>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v>心理专员</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SC_GRADE_L2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="C3" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="D3" t="str">
+        <v>20</v>
+      </c>
+      <c r="E3" t="str">
+        <v>筛查总分 &gt;= 38</v>
+      </c>
+      <c r="F3" t="str">
+        <v>L2</v>
+      </c>
+      <c r="G3" t="str">
+        <v>L2 年级协同</v>
+      </c>
+      <c r="H3" t="str">
+        <v>high</v>
+      </c>
+      <c r="I3" t="str">
+        <v>否</v>
+      </c>
+      <c r="J3" t="str">
+        <v>问题已超出单个教师可独立处理的范围，建议启动年级协同。</v>
+      </c>
+      <c r="K3" t="str">
+        <v>连续两次 L2</v>
+      </c>
+      <c r="L3" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M3" t="str">
+        <v>14天后复评</v>
+      </c>
+      <c r="N3" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SC_GRADE_L1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>999</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>L1</v>
+      </c>
+      <c r="G4" t="str">
+        <v>L1 教师支持</v>
+      </c>
+      <c r="H4" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I4" t="str">
+        <v>否</v>
+      </c>
+      <c r="J4" t="str">
+        <v>当前可由教师通过结构化观察和低压力谈话提供支持。</v>
+      </c>
+      <c r="K4" t="str">
+        <v>复评升级到 L2 或以上</v>
+      </c>
+      <c r="L4" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M4" t="str">
+        <v>30天后复评</v>
+      </c>
+      <c r="N4" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J2"/>
   <sheetData>
     <row r="1">
@@ -847,31 +1266,31 @@
         <v>student_case</v>
       </c>
       <c r="B2" t="str">
-        <v>题[q1] &gt;= 4 且 题[q3] &gt;= 4</v>
+        <v>题[adp2] &gt;= 5 且 题[emo2] &gt;= 5</v>
       </c>
       <c r="C2" t="str">
-        <v>行为与情绪双重危机，属学生个体问题模块红线</v>
+        <v>出现明显拒学或躯体化，且情绪已影响日常功能</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
       </c>
       <c r="E2" t="str">
-        <v>立即阻断常规建议输出，展示求助指引，生成转介工单通知心理专员</v>
+        <v>立即阻断常规建议输出，展示危机求助指引，生成转介工单通知心理专员</v>
       </c>
       <c r="F2" t="str">
-        <v>1. 停止当前评估流程 2. 展示危机求助指引 3. 自动创建安全事件 4. 生成转介工单 5. 发送短信通知心理专员</v>
+        <v>停止常规建议输出,展示危机求助指引,创建安全事件,生成转介工单,通知心理专员</v>
       </c>
       <c r="G2" t="str">
-        <v>当事教师完成心理专员面谈，且专员在系统中标记为「已处置」</v>
+        <v>心理专员完成评估并在系统中标记为「已处置」</v>
       </c>
       <c r="H2" t="str">
         <v>心理专员</v>
       </c>
       <c r="I2" t="str">
-        <v>[教师姓名]老师在学生个体问题评估中触发红线：行为与情绪双重危机。请尽快登录系统查看工单。</v>
+        <v>[学生]个体问题评估触发红线：出现拒学与情绪功能受损。请尽快介入。</v>
       </c>
       <c r="J2" t="str">
-        <v>PRD 8.3</v>
+        <v>学生个体问题手册v1</v>
       </c>
     </row>
   </sheetData>

--- a/business-libraries/test-data/student_case/attribution.xlsx
+++ b/business-libraries/test-data/student_case/attribution.xlsx
@@ -1040,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1176,51 +1176,139 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SC_GRADE_L1</v>
+        <v>SC_GRADE_EBRCA_L3</v>
       </c>
       <c r="B4" t="str">
         <v>student_case</v>
       </c>
       <c r="C4" t="str">
+        <v>SC_EBRCA</v>
+      </c>
+      <c r="D4" t="str">
+        <v>15</v>
+      </c>
+      <c r="E4" t="str">
+        <v>均分 &gt;= 4</v>
+      </c>
+      <c r="F4" t="str">
+        <v>L3</v>
+      </c>
+      <c r="G4" t="str">
+        <v>L3 专业会商</v>
+      </c>
+      <c r="H4" t="str">
+        <v>crisis</v>
+      </c>
+      <c r="I4" t="str">
+        <v>是</v>
+      </c>
+      <c r="J4" t="str">
+        <v>结构化观察显示功能影响明显且既有支持无效，已达专业会商层级。</v>
+      </c>
+      <c r="K4" t="str">
         <v/>
       </c>
-      <c r="D4" t="str">
+      <c r="L4" t="str">
+        <v>心理专员</v>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>SC_GRADE_EBRCA_L2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="C5" t="str">
+        <v>SC_EBRCA</v>
+      </c>
+      <c r="D5" t="str">
+        <v>25</v>
+      </c>
+      <c r="E5" t="str">
+        <v>均分 &gt;= 3</v>
+      </c>
+      <c r="F5" t="str">
+        <v>L2</v>
+      </c>
+      <c r="G5" t="str">
+        <v>L2 年级协同</v>
+      </c>
+      <c r="H5" t="str">
+        <v>high</v>
+      </c>
+      <c r="I5" t="str">
+        <v>否</v>
+      </c>
+      <c r="J5" t="str">
+        <v>结构化观察显示需要年级协同，建议整理材料后共同制定支持方案。</v>
+      </c>
+      <c r="K5" t="str">
+        <v>连续两次 L2</v>
+      </c>
+      <c r="L5" t="str">
+        <v>年级组长</v>
+      </c>
+      <c r="M5" t="str">
+        <v>14天后复评</v>
+      </c>
+      <c r="N5" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>SC_GRADE_L1</v>
+      </c>
+      <c r="B6" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
         <v>999</v>
       </c>
-      <c r="E4" t="str">
+      <c r="E6" t="str">
         <v/>
       </c>
-      <c r="F4" t="str">
+      <c r="F6" t="str">
         <v>L1</v>
       </c>
-      <c r="G4" t="str">
+      <c r="G6" t="str">
         <v>L1 教师支持</v>
       </c>
-      <c r="H4" t="str">
+      <c r="H6" t="str">
         <v>medium</v>
       </c>
-      <c r="I4" t="str">
+      <c r="I6" t="str">
         <v>否</v>
       </c>
-      <c r="J4" t="str">
+      <c r="J6" t="str">
         <v>当前可由教师通过结构化观察和低压力谈话提供支持。</v>
       </c>
-      <c r="K4" t="str">
+      <c r="K6" t="str">
         <v>复评升级到 L2 或以上</v>
       </c>
-      <c r="L4" t="str">
+      <c r="L6" t="str">
         <v>年级组长</v>
       </c>
-      <c r="M4" t="str">
+      <c r="M6" t="str">
         <v>30天后复评</v>
       </c>
-      <c r="N4" t="str">
+      <c r="N6" t="str">
         <v>学生个体问题手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N6"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/business-libraries/test-data/student_case/attribution.xlsx
+++ b/business-libraries/test-data/student_case/attribution.xlsx
@@ -437,10 +437,10 @@
         <v>总分</v>
       </c>
       <c r="D2" t="str">
-        <v>五类筛查总分</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -494,7 +494,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SC_AT_EMOTION</v>
+        <v>SC_AT_01</v>
       </c>
       <c r="B2" t="str">
         <v>情绪调节困难</v>
@@ -526,7 +526,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SC_AT_BEHAVIOR</v>
+        <v>SC_AT_02</v>
       </c>
       <c r="B3" t="str">
         <v>行为调控困难</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SC_AT_SOCIAL</v>
+        <v>SC_AT_03</v>
       </c>
       <c r="B4" t="str">
         <v>同伴关系受损</v>
@@ -590,7 +590,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SC_AT_ACADEMIC</v>
+        <v>SC_AT_04</v>
       </c>
       <c r="B5" t="str">
         <v>学业功能下降</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SC_AT_ADAPT</v>
+        <v>SC_AT_05</v>
       </c>
       <c r="B6" t="str">
         <v>适应障碍信号</v>
@@ -691,13 +691,13 @@
         <v>SC_EV_01</v>
       </c>
       <c r="B2" t="str">
-        <v>SC_AT_EMOTION</v>
+        <v>SC_AT_01</v>
       </c>
       <c r="C2" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D2" t="str">
-        <v>维度[SC_EMOTION] &gt;= 4</v>
+        <v>维度[SC_S1D3] &gt;= 4</v>
       </c>
       <c r="E2" t="str">
         <v>3</v>
@@ -714,13 +714,13 @@
         <v>SC_EV_02</v>
       </c>
       <c r="B3" t="str">
-        <v>SC_AT_EMOTION</v>
+        <v>SC_AT_01</v>
       </c>
       <c r="C3" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D3" t="str">
-        <v>维度[SC_EMOTION] &gt;= 3</v>
+        <v>维度[SC_S1D3] &gt;= 3</v>
       </c>
       <c r="E3" t="str">
         <v>1</v>
@@ -737,13 +737,13 @@
         <v>SC_EV_03</v>
       </c>
       <c r="B4" t="str">
-        <v>SC_AT_BEHAVIOR</v>
+        <v>SC_AT_02</v>
       </c>
       <c r="C4" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D4" t="str">
-        <v>维度[SC_BEHAVIOR] &gt;= 4</v>
+        <v>维度[SC_S1D2] &gt;= 4</v>
       </c>
       <c r="E4" t="str">
         <v>3</v>
@@ -760,13 +760,13 @@
         <v>SC_EV_04</v>
       </c>
       <c r="B5" t="str">
-        <v>SC_AT_BEHAVIOR</v>
+        <v>SC_AT_02</v>
       </c>
       <c r="C5" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D5" t="str">
-        <v>维度[SC_BEHAVIOR] &gt;= 3</v>
+        <v>维度[SC_S1D2] &gt;= 3</v>
       </c>
       <c r="E5" t="str">
         <v>1</v>
@@ -783,13 +783,13 @@
         <v>SC_EV_05</v>
       </c>
       <c r="B6" t="str">
-        <v>SC_AT_SOCIAL</v>
+        <v>SC_AT_03</v>
       </c>
       <c r="C6" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D6" t="str">
-        <v>维度[SC_SOCIAL] &gt;= 4</v>
+        <v>维度[SC_S1D4] &gt;= 4</v>
       </c>
       <c r="E6" t="str">
         <v>2.5</v>
@@ -806,13 +806,13 @@
         <v>SC_EV_06</v>
       </c>
       <c r="B7" t="str">
-        <v>SC_AT_SOCIAL</v>
+        <v>SC_AT_03</v>
       </c>
       <c r="C7" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D7" t="str">
-        <v>维度[SC_SOCIAL] &gt;= 3</v>
+        <v>维度[SC_S1D4] &gt;= 3</v>
       </c>
       <c r="E7" t="str">
         <v>1</v>
@@ -829,13 +829,13 @@
         <v>SC_EV_07</v>
       </c>
       <c r="B8" t="str">
-        <v>SC_AT_ACADEMIC</v>
+        <v>SC_AT_04</v>
       </c>
       <c r="C8" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D8" t="str">
-        <v>维度[SC_ACADEMIC] &gt;= 4</v>
+        <v>维度[SC_S1D1] &gt;= 4</v>
       </c>
       <c r="E8" t="str">
         <v>2.5</v>
@@ -852,13 +852,13 @@
         <v>SC_EV_08</v>
       </c>
       <c r="B9" t="str">
-        <v>SC_AT_ACADEMIC</v>
+        <v>SC_AT_04</v>
       </c>
       <c r="C9" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D9" t="str">
-        <v>维度[SC_ACADEMIC] &gt;= 3</v>
+        <v>维度[SC_S1D1] &gt;= 3</v>
       </c>
       <c r="E9" t="str">
         <v>1</v>
@@ -875,13 +875,13 @@
         <v>SC_EV_09</v>
       </c>
       <c r="B10" t="str">
-        <v>SC_AT_ADAPT</v>
+        <v>SC_AT_05</v>
       </c>
       <c r="C10" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D10" t="str">
-        <v>维度[SC_ADAPT] &gt;= 4</v>
+        <v>维度[SC_S1D5] &gt;= 4</v>
       </c>
       <c r="E10" t="str">
         <v>3.5</v>
@@ -898,13 +898,13 @@
         <v>SC_EV_10</v>
       </c>
       <c r="B11" t="str">
-        <v>SC_AT_ADAPT</v>
+        <v>SC_AT_05</v>
       </c>
       <c r="C11" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D11" t="str">
-        <v>题[adp3] &gt;= 4</v>
+        <v>题[q15] &gt;= 4</v>
       </c>
       <c r="E11" t="str">
         <v>2</v>
@@ -921,13 +921,13 @@
         <v>SC_EV_11</v>
       </c>
       <c r="B12" t="str">
-        <v>SC_AT_ADAPT</v>
+        <v>SC_AT_05</v>
       </c>
       <c r="C12" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D12" t="str">
-        <v>维度[SC_ADAPT] &gt;= 3</v>
+        <v>维度[SC_S1D5] &gt;= 3</v>
       </c>
       <c r="E12" t="str">
         <v>1</v>
@@ -941,16 +941,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SC_EV_21</v>
+        <v>SC_EV_12</v>
       </c>
       <c r="B13" t="str">
-        <v>SC_AT_BEHAVIOR</v>
+        <v>SC_AT_02</v>
       </c>
       <c r="C13" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="D13" t="str">
-        <v>维度[SC_TRIGGER] &gt;= 3.5</v>
+        <v>维度[SC_S2D1] &gt;= 3.5</v>
       </c>
       <c r="E13" t="str">
         <v>2.5</v>
@@ -964,16 +964,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SC_EV_22</v>
+        <v>SC_EV_13</v>
       </c>
       <c r="B14" t="str">
-        <v>SC_AT_ADAPT</v>
+        <v>SC_AT_05</v>
       </c>
       <c r="C14" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="D14" t="str">
-        <v>维度[SC_FUNCTION] &gt;= 3.5</v>
+        <v>维度[SC_S2D2] &gt;= 3.5</v>
       </c>
       <c r="E14" t="str">
         <v>3</v>
@@ -987,16 +987,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SC_EV_23</v>
+        <v>SC_EV_14</v>
       </c>
       <c r="B15" t="str">
-        <v>SC_AT_EMOTION</v>
+        <v>SC_AT_01</v>
       </c>
       <c r="C15" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="D15" t="str">
-        <v>维度[SC_SUPPORT_TRIED] &gt;= 3.5</v>
+        <v>维度[SC_S2D3] &gt;= 3.5</v>
       </c>
       <c r="E15" t="str">
         <v>2.5</v>
@@ -1010,16 +1010,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SC_EV_24</v>
+        <v>SC_EV_15</v>
       </c>
       <c r="B16" t="str">
-        <v>SC_AT_SOCIAL</v>
+        <v>SC_AT_03</v>
       </c>
       <c r="C16" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="D16" t="str">
-        <v>维度[SC_FUNCTION] &gt;= 3</v>
+        <v>维度[SC_S2D2] &gt;= 3</v>
       </c>
       <c r="E16" t="str">
         <v>1.5</v>
@@ -1040,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1088,22 +1088,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SC_GRADE_L3</v>
+        <v>SC_GR_01</v>
       </c>
       <c r="B2" t="str">
         <v>student_case</v>
       </c>
       <c r="C2" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D2" t="str">
         <v>10</v>
       </c>
       <c r="E2" t="str">
-        <v>筛查总分 &gt;= 52</v>
+        <v>总分 &gt;= 52</v>
       </c>
       <c r="F2" t="str">
-        <v>L3</v>
+        <v>red</v>
       </c>
       <c r="G2" t="str">
         <v>L3 专业会商</v>
@@ -1132,22 +1132,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SC_GRADE_L2</v>
+        <v>SC_GR_02</v>
       </c>
       <c r="B3" t="str">
         <v>student_case</v>
       </c>
       <c r="C3" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D3" t="str">
         <v>20</v>
       </c>
       <c r="E3" t="str">
-        <v>筛查总分 &gt;= 38</v>
+        <v>总分 &gt;= 38</v>
       </c>
       <c r="F3" t="str">
-        <v>L2</v>
+        <v>orange</v>
       </c>
       <c r="G3" t="str">
         <v>L2 年级协同</v>
@@ -1176,40 +1176,40 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SC_GRADE_EBRCA_L3</v>
+        <v>SC_GR_03</v>
       </c>
       <c r="B4" t="str">
         <v>student_case</v>
       </c>
       <c r="C4" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S1</v>
       </c>
       <c r="D4" t="str">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E4" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>总分 &gt;= 25</v>
       </c>
       <c r="F4" t="str">
-        <v>L3</v>
+        <v>yellow</v>
       </c>
       <c r="G4" t="str">
-        <v>L3 专业会商</v>
+        <v>L1 教师关注</v>
       </c>
       <c r="H4" t="str">
-        <v>crisis</v>
+        <v>medium</v>
       </c>
       <c r="I4" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J4" t="str">
-        <v>结构化观察显示功能影响明显且既有支持无效，已达专业会商层级。</v>
+        <v>总分处于关注区间，暂不需要年级协同</v>
       </c>
       <c r="K4" t="str">
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>心理专员</v>
+        <v/>
       </c>
       <c r="M4" t="str">
         <v/>
@@ -1220,22 +1220,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SC_GRADE_EBRCA_L2</v>
+        <v>SC_GR_AUTO_01</v>
       </c>
       <c r="B5" t="str">
         <v>student_case</v>
       </c>
       <c r="C5" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="D5" t="str">
-        <v>25</v>
+        <v>501</v>
       </c>
       <c r="E5" t="str">
-        <v>均分 &gt;= 3</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F5" t="str">
-        <v>L2</v>
+        <v>orange</v>
       </c>
       <c r="G5" t="str">
         <v>L2 年级协同</v>
@@ -1247,16 +1247,16 @@
         <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>结构化观察显示需要年级协同，建议整理材料后共同制定支持方案。</v>
+        <v>问题已超出单个教师可独立处理的范围，建议启动年级协同。</v>
       </c>
       <c r="K5" t="str">
-        <v>连续两次 L2</v>
+        <v/>
       </c>
       <c r="L5" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M5" t="str">
-        <v>14天后复评</v>
+        <v/>
       </c>
       <c r="N5" t="str">
         <v>学生个体问题手册v1</v>
@@ -1264,25 +1264,25 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SC_GRADE_L1</v>
+        <v>SC_GR_AUTO_02</v>
       </c>
       <c r="B6" t="str">
         <v>student_case</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>SC_S2</v>
       </c>
       <c r="D6" t="str">
-        <v>999</v>
+        <v>502</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>均分 &gt;= 3.5</v>
       </c>
       <c r="F6" t="str">
-        <v>L1</v>
+        <v>yellow</v>
       </c>
       <c r="G6" t="str">
-        <v>L1 教师支持</v>
+        <v>L1 教师关注</v>
       </c>
       <c r="H6" t="str">
         <v>medium</v>
@@ -1291,24 +1291,68 @@
         <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>当前可由教师通过结构化观察和低压力谈话提供支持。</v>
+        <v>总分处于关注区间，暂不需要年级协同</v>
       </c>
       <c r="K6" t="str">
-        <v>复评升级到 L2 或以上</v>
+        <v/>
       </c>
       <c r="L6" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M6" t="str">
-        <v>30天后复评</v>
+        <v/>
       </c>
       <c r="N6" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>SC_GR_DEFAULT</v>
+      </c>
+      <c r="B7" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>999</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>green</v>
+      </c>
+      <c r="G7" t="str">
+        <v>L1 教师支持</v>
+      </c>
+      <c r="H7" t="str">
+        <v>low</v>
+      </c>
+      <c r="I7" t="str">
+        <v>否</v>
+      </c>
+      <c r="J7" t="str">
+        <v>本次评估未发现需要重点干预的信号</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
         <v>学生个体问题手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1354,10 +1398,10 @@
         <v>student_case</v>
       </c>
       <c r="B2" t="str">
-        <v>题[adp2] &gt;= 5 且 题[emo2] &gt;= 5</v>
+        <v>总分 &gt;= 52</v>
       </c>
       <c r="C2" t="str">
-        <v>出现明显拒学或躯体化，且情绪已影响日常功能</v>
+        <v>多个维度同时处于高位，已达到专业会商层级，请整理材料并启动转介。</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
@@ -1366,7 +1410,7 @@
         <v>立即阻断常规建议输出，展示危机求助指引，生成转介工单通知心理专员</v>
       </c>
       <c r="F2" t="str">
-        <v>停止常规建议输出,展示危机求助指引,创建安全事件,生成转介工单,通知心理专员</v>
+        <v>停止常规建议输出；展示危机求助指引；创建安全事件；生成转介工单；通知心理专员</v>
       </c>
       <c r="G2" t="str">
         <v>心理专员完成评估并在系统中标记为「已处置」</v>

--- a/business-libraries/test-data/student_case/attribution.xlsx
+++ b/business-libraries/test-data/student_case/attribution.xlsx
@@ -437,10 +437,10 @@
         <v>总分</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>五类筛查总分</v>
       </c>
       <c r="E2" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -494,7 +494,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SC_AT_01</v>
+        <v>SC_AT_EMOTION</v>
       </c>
       <c r="B2" t="str">
         <v>情绪调节困难</v>
@@ -526,7 +526,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SC_AT_02</v>
+        <v>SC_AT_BEHAVIOR</v>
       </c>
       <c r="B3" t="str">
         <v>行为调控困难</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SC_AT_03</v>
+        <v>SC_AT_SOCIAL</v>
       </c>
       <c r="B4" t="str">
         <v>同伴关系受损</v>
@@ -590,7 +590,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SC_AT_04</v>
+        <v>SC_AT_ACADEMIC</v>
       </c>
       <c r="B5" t="str">
         <v>学业功能下降</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SC_AT_05</v>
+        <v>SC_AT_ADAPT</v>
       </c>
       <c r="B6" t="str">
         <v>适应障碍信号</v>
@@ -691,13 +691,13 @@
         <v>SC_EV_01</v>
       </c>
       <c r="B2" t="str">
-        <v>SC_AT_01</v>
+        <v>SC_AT_EMOTION</v>
       </c>
       <c r="C2" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="D2" t="str">
-        <v>维度[SC_S1D3] &gt;= 4</v>
+        <v>维度[SC_EMOTION] &gt;= 4</v>
       </c>
       <c r="E2" t="str">
         <v>3</v>
@@ -714,13 +714,13 @@
         <v>SC_EV_02</v>
       </c>
       <c r="B3" t="str">
-        <v>SC_AT_01</v>
+        <v>SC_AT_EMOTION</v>
       </c>
       <c r="C3" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="D3" t="str">
-        <v>维度[SC_S1D3] &gt;= 3</v>
+        <v>维度[SC_EMOTION] &gt;= 3</v>
       </c>
       <c r="E3" t="str">
         <v>1</v>
@@ -737,13 +737,13 @@
         <v>SC_EV_03</v>
       </c>
       <c r="B4" t="str">
-        <v>SC_AT_02</v>
+        <v>SC_AT_BEHAVIOR</v>
       </c>
       <c r="C4" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="D4" t="str">
-        <v>维度[SC_S1D2] &gt;= 4</v>
+        <v>维度[SC_BEHAVIOR] &gt;= 4</v>
       </c>
       <c r="E4" t="str">
         <v>3</v>
@@ -760,13 +760,13 @@
         <v>SC_EV_04</v>
       </c>
       <c r="B5" t="str">
-        <v>SC_AT_02</v>
+        <v>SC_AT_BEHAVIOR</v>
       </c>
       <c r="C5" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="D5" t="str">
-        <v>维度[SC_S1D2] &gt;= 3</v>
+        <v>维度[SC_BEHAVIOR] &gt;= 3</v>
       </c>
       <c r="E5" t="str">
         <v>1</v>
@@ -783,13 +783,13 @@
         <v>SC_EV_05</v>
       </c>
       <c r="B6" t="str">
-        <v>SC_AT_03</v>
+        <v>SC_AT_SOCIAL</v>
       </c>
       <c r="C6" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="D6" t="str">
-        <v>维度[SC_S1D4] &gt;= 4</v>
+        <v>维度[SC_SOCIAL] &gt;= 4</v>
       </c>
       <c r="E6" t="str">
         <v>2.5</v>
@@ -806,13 +806,13 @@
         <v>SC_EV_06</v>
       </c>
       <c r="B7" t="str">
-        <v>SC_AT_03</v>
+        <v>SC_AT_SOCIAL</v>
       </c>
       <c r="C7" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="D7" t="str">
-        <v>维度[SC_S1D4] &gt;= 3</v>
+        <v>维度[SC_SOCIAL] &gt;= 3</v>
       </c>
       <c r="E7" t="str">
         <v>1</v>
@@ -829,13 +829,13 @@
         <v>SC_EV_07</v>
       </c>
       <c r="B8" t="str">
-        <v>SC_AT_04</v>
+        <v>SC_AT_ACADEMIC</v>
       </c>
       <c r="C8" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="D8" t="str">
-        <v>维度[SC_S1D1] &gt;= 4</v>
+        <v>维度[SC_ACADEMIC] &gt;= 4</v>
       </c>
       <c r="E8" t="str">
         <v>2.5</v>
@@ -852,13 +852,13 @@
         <v>SC_EV_08</v>
       </c>
       <c r="B9" t="str">
-        <v>SC_AT_04</v>
+        <v>SC_AT_ACADEMIC</v>
       </c>
       <c r="C9" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="D9" t="str">
-        <v>维度[SC_S1D1] &gt;= 3</v>
+        <v>维度[SC_ACADEMIC] &gt;= 3</v>
       </c>
       <c r="E9" t="str">
         <v>1</v>
@@ -875,13 +875,13 @@
         <v>SC_EV_09</v>
       </c>
       <c r="B10" t="str">
-        <v>SC_AT_05</v>
+        <v>SC_AT_ADAPT</v>
       </c>
       <c r="C10" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="D10" t="str">
-        <v>维度[SC_S1D5] &gt;= 4</v>
+        <v>维度[SC_ADAPT] &gt;= 4</v>
       </c>
       <c r="E10" t="str">
         <v>3.5</v>
@@ -898,13 +898,13 @@
         <v>SC_EV_10</v>
       </c>
       <c r="B11" t="str">
-        <v>SC_AT_05</v>
+        <v>SC_AT_ADAPT</v>
       </c>
       <c r="C11" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="D11" t="str">
-        <v>题[q15] &gt;= 4</v>
+        <v>题[adp3] &gt;= 4</v>
       </c>
       <c r="E11" t="str">
         <v>2</v>
@@ -921,13 +921,13 @@
         <v>SC_EV_11</v>
       </c>
       <c r="B12" t="str">
-        <v>SC_AT_05</v>
+        <v>SC_AT_ADAPT</v>
       </c>
       <c r="C12" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="D12" t="str">
-        <v>维度[SC_S1D5] &gt;= 3</v>
+        <v>维度[SC_ADAPT] &gt;= 3</v>
       </c>
       <c r="E12" t="str">
         <v>1</v>
@@ -941,16 +941,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SC_EV_12</v>
+        <v>SC_EV_21</v>
       </c>
       <c r="B13" t="str">
-        <v>SC_AT_02</v>
+        <v>SC_AT_BEHAVIOR</v>
       </c>
       <c r="C13" t="str">
-        <v>SC_S2</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="D13" t="str">
-        <v>维度[SC_S2D1] &gt;= 3.5</v>
+        <v>维度[SC_TRIGGER] &gt;= 3.5</v>
       </c>
       <c r="E13" t="str">
         <v>2.5</v>
@@ -964,16 +964,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SC_EV_13</v>
+        <v>SC_EV_22</v>
       </c>
       <c r="B14" t="str">
-        <v>SC_AT_05</v>
+        <v>SC_AT_ADAPT</v>
       </c>
       <c r="C14" t="str">
-        <v>SC_S2</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="D14" t="str">
-        <v>维度[SC_S2D2] &gt;= 3.5</v>
+        <v>维度[SC_FUNCTION] &gt;= 3.5</v>
       </c>
       <c r="E14" t="str">
         <v>3</v>
@@ -987,16 +987,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SC_EV_14</v>
+        <v>SC_EV_23</v>
       </c>
       <c r="B15" t="str">
-        <v>SC_AT_01</v>
+        <v>SC_AT_EMOTION</v>
       </c>
       <c r="C15" t="str">
-        <v>SC_S2</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="D15" t="str">
-        <v>维度[SC_S2D3] &gt;= 3.5</v>
+        <v>维度[SC_SUPPORT_TRIED] &gt;= 3.5</v>
       </c>
       <c r="E15" t="str">
         <v>2.5</v>
@@ -1010,16 +1010,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SC_EV_15</v>
+        <v>SC_EV_24</v>
       </c>
       <c r="B16" t="str">
-        <v>SC_AT_03</v>
+        <v>SC_AT_SOCIAL</v>
       </c>
       <c r="C16" t="str">
-        <v>SC_S2</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="D16" t="str">
-        <v>维度[SC_S2D2] &gt;= 3</v>
+        <v>维度[SC_FUNCTION] &gt;= 3</v>
       </c>
       <c r="E16" t="str">
         <v>1.5</v>
@@ -1040,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:P6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1083,27 +1083,33 @@
         <v>复评触发条件</v>
       </c>
       <c r="N1" t="str">
+        <v>干预工具</v>
+      </c>
+      <c r="O1" t="str">
+        <v>干预动作</v>
+      </c>
+      <c r="P1" t="str">
         <v>手册出处</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SC_GR_01</v>
+        <v>SC_GRADE_L3</v>
       </c>
       <c r="B2" t="str">
         <v>student_case</v>
       </c>
       <c r="C2" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="D2" t="str">
         <v>10</v>
       </c>
       <c r="E2" t="str">
-        <v>总分 &gt;= 52</v>
+        <v>筛查总分 &gt;= 52</v>
       </c>
       <c r="F2" t="str">
-        <v>red</v>
+        <v>L3</v>
       </c>
       <c r="G2" t="str">
         <v>L3 专业会商</v>
@@ -1127,27 +1133,33 @@
         <v/>
       </c>
       <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
         <v>学生个体问题手册v1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SC_GR_02</v>
+        <v>SC_GRADE_L2</v>
       </c>
       <c r="B3" t="str">
         <v>student_case</v>
       </c>
       <c r="C3" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="D3" t="str">
         <v>20</v>
       </c>
       <c r="E3" t="str">
-        <v>总分 &gt;= 38</v>
+        <v>筛查总分 &gt;= 38</v>
       </c>
       <c r="F3" t="str">
-        <v>orange</v>
+        <v>L2</v>
       </c>
       <c r="G3" t="str">
         <v>L2 年级协同</v>
@@ -1171,71 +1183,83 @@
         <v>14天后复评</v>
       </c>
       <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
         <v>学生个体问题手册v1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SC_GR_03</v>
+        <v>SC_GRADE_EBRCA_L3</v>
       </c>
       <c r="B4" t="str">
         <v>student_case</v>
       </c>
       <c r="C4" t="str">
-        <v>SC_S1</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="D4" t="str">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E4" t="str">
-        <v>总分 &gt;= 25</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F4" t="str">
-        <v>yellow</v>
+        <v>L3</v>
       </c>
       <c r="G4" t="str">
-        <v>L1 教师关注</v>
+        <v>L3 专业会商</v>
       </c>
       <c r="H4" t="str">
-        <v>medium</v>
+        <v>crisis</v>
       </c>
       <c r="I4" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J4" t="str">
-        <v>总分处于关注区间，暂不需要年级协同</v>
+        <v>结构化观察显示功能影响明显且既有支持无效，已达专业会商层级。</v>
       </c>
       <c r="K4" t="str">
         <v/>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>心理专员</v>
       </c>
       <c r="M4" t="str">
         <v/>
       </c>
       <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
         <v>学生个体问题手册v1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SC_GR_AUTO_01</v>
+        <v>SC_GRADE_EBRCA_L2</v>
       </c>
       <c r="B5" t="str">
         <v>student_case</v>
       </c>
       <c r="C5" t="str">
-        <v>SC_S2</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="D5" t="str">
-        <v>501</v>
+        <v>25</v>
       </c>
       <c r="E5" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>均分 &gt;= 3</v>
       </c>
       <c r="F5" t="str">
-        <v>orange</v>
+        <v>L2</v>
       </c>
       <c r="G5" t="str">
         <v>L2 年级协同</v>
@@ -1247,42 +1271,48 @@
         <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>问题已超出单个教师可独立处理的范围，建议启动年级协同。</v>
+        <v>结构化观察显示需要年级协同，建议整理材料后共同制定支持方案。</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>连续两次 L2</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>年级组长</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>14天后复评</v>
       </c>
       <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
         <v>学生个体问题手册v1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SC_GR_AUTO_02</v>
+        <v>SC_GRADE_L1</v>
       </c>
       <c r="B6" t="str">
         <v>student_case</v>
       </c>
       <c r="C6" t="str">
-        <v>SC_S2</v>
+        <v/>
       </c>
       <c r="D6" t="str">
-        <v>502</v>
+        <v>999</v>
       </c>
       <c r="E6" t="str">
-        <v>均分 &gt;= 3.5</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>yellow</v>
+        <v>L1</v>
       </c>
       <c r="G6" t="str">
-        <v>L1 教师关注</v>
+        <v>L1 教师支持</v>
       </c>
       <c r="H6" t="str">
         <v>medium</v>
@@ -1291,68 +1321,30 @@
         <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>总分处于关注区间，暂不需要年级协同</v>
+        <v>当前可由教师通过结构化观察和低压力谈话提供支持。</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>复评升级到 L2 或以上</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>年级组长</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>30天后复评</v>
       </c>
       <c r="N6" t="str">
-        <v>学生个体问题手册v1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>SC_GR_DEFAULT</v>
-      </c>
-      <c r="B7" t="str">
-        <v>student_case</v>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v>999</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v>green</v>
-      </c>
-      <c r="G7" t="str">
-        <v>L1 教师支持</v>
-      </c>
-      <c r="H7" t="str">
-        <v>low</v>
-      </c>
-      <c r="I7" t="str">
-        <v>否</v>
-      </c>
-      <c r="J7" t="str">
-        <v>本次评估未发现需要重点干预的信号</v>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
-        <v/>
-      </c>
-      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
         <v>学生个体问题手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1398,10 +1390,10 @@
         <v>student_case</v>
       </c>
       <c r="B2" t="str">
-        <v>总分 &gt;= 52</v>
+        <v>题[adp2] &gt;= 5 且 题[emo2] &gt;= 5</v>
       </c>
       <c r="C2" t="str">
-        <v>多个维度同时处于高位，已达到专业会商层级，请整理材料并启动转介。</v>
+        <v>出现明显拒学或躯体化，且情绪已影响日常功能</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
@@ -1410,7 +1402,7 @@
         <v>立即阻断常规建议输出，展示危机求助指引，生成转介工单通知心理专员</v>
       </c>
       <c r="F2" t="str">
-        <v>停止常规建议输出；展示危机求助指引；创建安全事件；生成转介工单；通知心理专员</v>
+        <v>停止常规建议输出,展示危机求助指引,创建安全事件,生成转介工单,通知心理专员</v>
       </c>
       <c r="G2" t="str">
         <v>心理专员完成评估并在系统中标记为「已处置」</v>

--- a/business-libraries/test-data/student_case/attribution.xlsx
+++ b/business-libraries/test-data/student_case/attribution.xlsx
@@ -437,10 +437,10 @@
         <v>总分</v>
       </c>
       <c r="D2" t="str">
-        <v>五类筛查总分</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -494,7 +494,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SC_AT_EMOTION</v>
+        <v>SC_AT_01</v>
       </c>
       <c r="B2" t="str">
         <v>情绪调节困难</v>
@@ -526,7 +526,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SC_AT_BEHAVIOR</v>
+        <v>SC_AT_02</v>
       </c>
       <c r="B3" t="str">
         <v>行为调控困难</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SC_AT_SOCIAL</v>
+        <v>SC_AT_03</v>
       </c>
       <c r="B4" t="str">
         <v>同伴关系受损</v>
@@ -590,7 +590,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SC_AT_ACADEMIC</v>
+        <v>SC_AT_04</v>
       </c>
       <c r="B5" t="str">
         <v>学业功能下降</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SC_AT_ADAPT</v>
+        <v>SC_AT_05</v>
       </c>
       <c r="B6" t="str">
         <v>适应障碍信号</v>
@@ -691,13 +691,13 @@
         <v>SC_EV_01</v>
       </c>
       <c r="B2" t="str">
-        <v>SC_AT_EMOTION</v>
+        <v>SC_AT_01</v>
       </c>
       <c r="C2" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D2" t="str">
-        <v>维度[SC_EMOTION] &gt;= 4</v>
+        <v>维度[SC_S1D3] &gt;= 4</v>
       </c>
       <c r="E2" t="str">
         <v>3</v>
@@ -714,13 +714,13 @@
         <v>SC_EV_02</v>
       </c>
       <c r="B3" t="str">
-        <v>SC_AT_EMOTION</v>
+        <v>SC_AT_01</v>
       </c>
       <c r="C3" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D3" t="str">
-        <v>维度[SC_EMOTION] &gt;= 3</v>
+        <v>维度[SC_S1D3] &gt;= 3</v>
       </c>
       <c r="E3" t="str">
         <v>1</v>
@@ -737,13 +737,13 @@
         <v>SC_EV_03</v>
       </c>
       <c r="B4" t="str">
-        <v>SC_AT_BEHAVIOR</v>
+        <v>SC_AT_02</v>
       </c>
       <c r="C4" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D4" t="str">
-        <v>维度[SC_BEHAVIOR] &gt;= 4</v>
+        <v>维度[SC_S1D2] &gt;= 4</v>
       </c>
       <c r="E4" t="str">
         <v>3</v>
@@ -760,13 +760,13 @@
         <v>SC_EV_04</v>
       </c>
       <c r="B5" t="str">
-        <v>SC_AT_BEHAVIOR</v>
+        <v>SC_AT_02</v>
       </c>
       <c r="C5" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D5" t="str">
-        <v>维度[SC_BEHAVIOR] &gt;= 3</v>
+        <v>维度[SC_S1D2] &gt;= 3</v>
       </c>
       <c r="E5" t="str">
         <v>1</v>
@@ -783,13 +783,13 @@
         <v>SC_EV_05</v>
       </c>
       <c r="B6" t="str">
-        <v>SC_AT_SOCIAL</v>
+        <v>SC_AT_03</v>
       </c>
       <c r="C6" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D6" t="str">
-        <v>维度[SC_SOCIAL] &gt;= 4</v>
+        <v>维度[SC_S1D4] &gt;= 4</v>
       </c>
       <c r="E6" t="str">
         <v>2.5</v>
@@ -806,13 +806,13 @@
         <v>SC_EV_06</v>
       </c>
       <c r="B7" t="str">
-        <v>SC_AT_SOCIAL</v>
+        <v>SC_AT_03</v>
       </c>
       <c r="C7" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D7" t="str">
-        <v>维度[SC_SOCIAL] &gt;= 3</v>
+        <v>维度[SC_S1D4] &gt;= 3</v>
       </c>
       <c r="E7" t="str">
         <v>1</v>
@@ -829,13 +829,13 @@
         <v>SC_EV_07</v>
       </c>
       <c r="B8" t="str">
-        <v>SC_AT_ACADEMIC</v>
+        <v>SC_AT_04</v>
       </c>
       <c r="C8" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D8" t="str">
-        <v>维度[SC_ACADEMIC] &gt;= 4</v>
+        <v>维度[SC_S1D1] &gt;= 4</v>
       </c>
       <c r="E8" t="str">
         <v>2.5</v>
@@ -852,13 +852,13 @@
         <v>SC_EV_08</v>
       </c>
       <c r="B9" t="str">
-        <v>SC_AT_ACADEMIC</v>
+        <v>SC_AT_04</v>
       </c>
       <c r="C9" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D9" t="str">
-        <v>维度[SC_ACADEMIC] &gt;= 3</v>
+        <v>维度[SC_S1D1] &gt;= 3</v>
       </c>
       <c r="E9" t="str">
         <v>1</v>
@@ -875,13 +875,13 @@
         <v>SC_EV_09</v>
       </c>
       <c r="B10" t="str">
-        <v>SC_AT_ADAPT</v>
+        <v>SC_AT_05</v>
       </c>
       <c r="C10" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D10" t="str">
-        <v>维度[SC_ADAPT] &gt;= 4</v>
+        <v>维度[SC_S1D5] &gt;= 4</v>
       </c>
       <c r="E10" t="str">
         <v>3.5</v>
@@ -898,13 +898,13 @@
         <v>SC_EV_10</v>
       </c>
       <c r="B11" t="str">
-        <v>SC_AT_ADAPT</v>
+        <v>SC_AT_05</v>
       </c>
       <c r="C11" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D11" t="str">
-        <v>题[adp3] &gt;= 4</v>
+        <v>题[q15] &gt;= 4</v>
       </c>
       <c r="E11" t="str">
         <v>2</v>
@@ -921,13 +921,13 @@
         <v>SC_EV_11</v>
       </c>
       <c r="B12" t="str">
-        <v>SC_AT_ADAPT</v>
+        <v>SC_AT_05</v>
       </c>
       <c r="C12" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D12" t="str">
-        <v>维度[SC_ADAPT] &gt;= 3</v>
+        <v>维度[SC_S1D5] &gt;= 3</v>
       </c>
       <c r="E12" t="str">
         <v>1</v>
@@ -941,16 +941,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SC_EV_21</v>
+        <v>SC_EV_12</v>
       </c>
       <c r="B13" t="str">
-        <v>SC_AT_BEHAVIOR</v>
+        <v>SC_AT_02</v>
       </c>
       <c r="C13" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="D13" t="str">
-        <v>维度[SC_TRIGGER] &gt;= 3.5</v>
+        <v>维度[SC_S2D1] &gt;= 3.5</v>
       </c>
       <c r="E13" t="str">
         <v>2.5</v>
@@ -964,16 +964,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SC_EV_22</v>
+        <v>SC_EV_13</v>
       </c>
       <c r="B14" t="str">
-        <v>SC_AT_ADAPT</v>
+        <v>SC_AT_05</v>
       </c>
       <c r="C14" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="D14" t="str">
-        <v>维度[SC_FUNCTION] &gt;= 3.5</v>
+        <v>维度[SC_S2D2] &gt;= 3.5</v>
       </c>
       <c r="E14" t="str">
         <v>3</v>
@@ -987,16 +987,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SC_EV_23</v>
+        <v>SC_EV_14</v>
       </c>
       <c r="B15" t="str">
-        <v>SC_AT_EMOTION</v>
+        <v>SC_AT_01</v>
       </c>
       <c r="C15" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="D15" t="str">
-        <v>维度[SC_SUPPORT_TRIED] &gt;= 3.5</v>
+        <v>维度[SC_S2D3] &gt;= 3.5</v>
       </c>
       <c r="E15" t="str">
         <v>2.5</v>
@@ -1010,16 +1010,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SC_EV_24</v>
+        <v>SC_EV_15</v>
       </c>
       <c r="B16" t="str">
-        <v>SC_AT_SOCIAL</v>
+        <v>SC_AT_03</v>
       </c>
       <c r="C16" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="D16" t="str">
-        <v>维度[SC_FUNCTION] &gt;= 3</v>
+        <v>维度[SC_S2D2] &gt;= 3</v>
       </c>
       <c r="E16" t="str">
         <v>1.5</v>
@@ -1040,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1094,22 +1094,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SC_GRADE_L3</v>
+        <v>SC_GR_01</v>
       </c>
       <c r="B2" t="str">
         <v>student_case</v>
       </c>
       <c r="C2" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D2" t="str">
         <v>10</v>
       </c>
       <c r="E2" t="str">
-        <v>筛查总分 &gt;= 52</v>
+        <v>总分 &gt;= 52</v>
       </c>
       <c r="F2" t="str">
-        <v>L3</v>
+        <v>red</v>
       </c>
       <c r="G2" t="str">
         <v>L3 专业会商</v>
@@ -1144,22 +1144,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SC_GRADE_L2</v>
+        <v>SC_GR_02</v>
       </c>
       <c r="B3" t="str">
         <v>student_case</v>
       </c>
       <c r="C3" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="D3" t="str">
         <v>20</v>
       </c>
       <c r="E3" t="str">
-        <v>筛查总分 &gt;= 38</v>
+        <v>总分 &gt;= 38</v>
       </c>
       <c r="F3" t="str">
-        <v>L2</v>
+        <v>orange</v>
       </c>
       <c r="G3" t="str">
         <v>L2 年级协同</v>
@@ -1194,40 +1194,40 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SC_GRADE_EBRCA_L3</v>
+        <v>SC_GR_03</v>
       </c>
       <c r="B4" t="str">
         <v>student_case</v>
       </c>
       <c r="C4" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S1</v>
       </c>
       <c r="D4" t="str">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E4" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>总分 &gt;= 25</v>
       </c>
       <c r="F4" t="str">
-        <v>L3</v>
+        <v>yellow</v>
       </c>
       <c r="G4" t="str">
-        <v>L3 专业会商</v>
+        <v>L1 教师关注</v>
       </c>
       <c r="H4" t="str">
-        <v>crisis</v>
+        <v>medium</v>
       </c>
       <c r="I4" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J4" t="str">
-        <v>结构化观察显示功能影响明显且既有支持无效，已达专业会商层级。</v>
+        <v>总分处于关注区间，暂不需要年级协同</v>
       </c>
       <c r="K4" t="str">
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>心理专员</v>
+        <v/>
       </c>
       <c r="M4" t="str">
         <v/>
@@ -1244,22 +1244,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SC_GRADE_EBRCA_L2</v>
+        <v>SC_GR_AUTO_01</v>
       </c>
       <c r="B5" t="str">
         <v>student_case</v>
       </c>
       <c r="C5" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="D5" t="str">
-        <v>25</v>
+        <v>501</v>
       </c>
       <c r="E5" t="str">
-        <v>均分 &gt;= 3</v>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F5" t="str">
-        <v>L2</v>
+        <v>orange</v>
       </c>
       <c r="G5" t="str">
         <v>L2 年级协同</v>
@@ -1271,16 +1271,16 @@
         <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>结构化观察显示需要年级协同，建议整理材料后共同制定支持方案。</v>
+        <v>问题已超出单个教师可独立处理的范围，建议启动年级协同。</v>
       </c>
       <c r="K5" t="str">
-        <v>连续两次 L2</v>
+        <v/>
       </c>
       <c r="L5" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M5" t="str">
-        <v>14天后复评</v>
+        <v/>
       </c>
       <c r="N5" t="str">
         <v/>
@@ -1294,25 +1294,25 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SC_GRADE_L1</v>
+        <v>SC_GR_AUTO_02</v>
       </c>
       <c r="B6" t="str">
         <v>student_case</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>SC_S2</v>
       </c>
       <c r="D6" t="str">
-        <v>999</v>
+        <v>502</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>均分 &gt;= 3.5</v>
       </c>
       <c r="F6" t="str">
-        <v>L1</v>
+        <v>yellow</v>
       </c>
       <c r="G6" t="str">
-        <v>L1 教师支持</v>
+        <v>L1 教师关注</v>
       </c>
       <c r="H6" t="str">
         <v>medium</v>
@@ -1321,16 +1321,16 @@
         <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>当前可由教师通过结构化观察和低压力谈话提供支持。</v>
+        <v>总分处于关注区间，暂不需要年级协同</v>
       </c>
       <c r="K6" t="str">
-        <v>复评升级到 L2 或以上</v>
+        <v/>
       </c>
       <c r="L6" t="str">
-        <v>年级组长</v>
+        <v/>
       </c>
       <c r="M6" t="str">
-        <v>30天后复评</v>
+        <v/>
       </c>
       <c r="N6" t="str">
         <v/>
@@ -1339,12 +1339,62 @@
         <v/>
       </c>
       <c r="P6" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>SC_GR_DEFAULT</v>
+      </c>
+      <c r="B7" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>999</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>green</v>
+      </c>
+      <c r="G7" t="str">
+        <v>L1 教师支持</v>
+      </c>
+      <c r="H7" t="str">
+        <v>low</v>
+      </c>
+      <c r="I7" t="str">
+        <v>否</v>
+      </c>
+      <c r="J7" t="str">
+        <v>本次评估未发现需要重点干预的信号</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
         <v>学生个体问题手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1390,10 +1440,10 @@
         <v>student_case</v>
       </c>
       <c r="B2" t="str">
-        <v>题[adp2] &gt;= 5 且 题[emo2] &gt;= 5</v>
+        <v>量表[SC_S1].总分 &gt;= 52</v>
       </c>
       <c r="C2" t="str">
-        <v>出现明显拒学或躯体化，且情绪已影响日常功能</v>
+        <v>多个维度同时处于高位，已达到专业会商层级，请整理材料并启动转介。</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
@@ -1402,7 +1452,7 @@
         <v>立即阻断常规建议输出，展示危机求助指引，生成转介工单通知心理专员</v>
       </c>
       <c r="F2" t="str">
-        <v>停止常规建议输出,展示危机求助指引,创建安全事件,生成转介工单,通知心理专员</v>
+        <v>停止常规建议输出；展示危机求助指引；创建安全事件；生成转介工单；通知心理专员</v>
       </c>
       <c r="G2" t="str">
         <v>心理专员完成评估并在系统中标记为「已处置」</v>

--- a/business-libraries/test-data/student_case/attribution.xlsx
+++ b/business-libraries/test-data/student_case/attribution.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -426,39 +426,16 @@
         <v>依赖维度编码</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>筛查总分</v>
-      </c>
-      <c r="B2" t="str">
-        <v>student_case</v>
-      </c>
-      <c r="C2" t="str">
-        <v>总分</v>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v>SC_S1</v>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -494,42 +471,42 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SC_AT_01</v>
+        <v>A1</v>
       </c>
       <c r="B2" t="str">
-        <v>情绪调节困难</v>
+        <v>注意力分散型</v>
       </c>
       <c r="C2" t="str">
         <v>student_case</v>
       </c>
       <c r="D2" t="str">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="E2" t="str">
-        <v>student_case,emotion</v>
+        <v>学习,student_case</v>
       </c>
       <c r="F2" t="str">
-        <v>学生持续出现低落、焦虑或退缩，且难以表达和调节当前感受。</v>
+        <v>课堂走神、玩文具、完不成课堂任务。核心机制是注意力维持困难而非不愿学</v>
       </c>
       <c r="G2" t="str">
-        <v>持续低落或易怒；很难说清自己的感受</v>
+        <v>课堂持续走神，需反复提醒；作业拖拉，完不成课堂任务</v>
       </c>
       <c r="H2" t="str">
-        <v>可能与家庭变化、同伴关系或学业压力相关</v>
+        <v>需区分发展性注意力波动（低年级正常）与病理性持续注意力缺陷；焦虑型依恋学生的走神可能是过度警觉</v>
       </c>
       <c r="I2" t="str">
-        <v>本周做一次低压力谈话，从可观察事实开始，不贴标签</v>
+        <v>用 T1 定时器分段法+关系锚定，或 T2 注意力信号约定开始干预</v>
       </c>
       <c r="J2" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SC_AT_02</v>
+        <v>A2</v>
       </c>
       <c r="B3" t="str">
-        <v>行为调控困难</v>
+        <v>动机缺失型</v>
       </c>
       <c r="C3" t="str">
         <v>student_case</v>
@@ -538,62 +515,62 @@
         <v>1.3</v>
       </c>
       <c r="E3" t="str">
-        <v>student_case,behavior</v>
+        <v>学习,student_case</v>
       </c>
       <c r="F3" t="str">
-        <v>冲动、对抗或规则破坏行为频繁出现，且诱因难以预测。</v>
+        <v>对学业失去兴趣，不做不交作业。核心机制是内在动机系统被长期挫败感破坏</v>
       </c>
       <c r="G3" t="str">
-        <v>行为频繁且场景不可预测；已影响他人学习</v>
+        <v>长期不交作业，对任何学科无兴趣</v>
       </c>
       <c r="H3" t="str">
-        <v>可能与执行功能、情绪调节或环境刺激相关</v>
+        <v>回避型依恋在学业中的典型表现：「反正做不好，不如不做」。不是懒，是习得性无助的自我防御</v>
       </c>
       <c r="I3" t="str">
-        <v>完成一周 ABC 结构化观察，记录行为前情境、行为本身和行为后结果</v>
+        <v>用 T11 优势锚定法（独立模式）通过优势通道激活学习动机</v>
       </c>
       <c r="J3" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SC_AT_03</v>
+        <v>A3</v>
       </c>
       <c r="B4" t="str">
-        <v>同伴关系受损</v>
+        <v>技能不足型</v>
       </c>
       <c r="C4" t="str">
         <v>student_case</v>
       </c>
       <c r="D4" t="str">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="str">
-        <v>student_case,social</v>
+        <v>学习,student_case</v>
       </c>
       <c r="F4" t="str">
-        <v>与同伴的冲突、排斥或孤立反复发生，缺少稳定的支持关系。</v>
+        <v>由于识字量、计算能力或学习方法落后导致的学业困难</v>
       </c>
       <c r="G4" t="str">
-        <v>被孤立或反复冲突；常规修复方式无效</v>
+        <v>特定科目持续不及格，识字量/计算能力落后</v>
       </c>
       <c r="H4" t="str">
-        <v>社交技能不足或班级关系结构问题</v>
+        <v>与家庭支持密切相关。E3（支持缺位）学生的 A3 风险显著更高</v>
       </c>
       <c r="I4" t="str">
-        <v>安排一次结构化的同伴配对活动，并观察互动质量</v>
+        <v>用 T11 优势锚定（适配学习策略）+ T3 渐进参与（学业版）分级提升</v>
       </c>
       <c r="J4" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SC_AT_04</v>
+        <v>B1</v>
       </c>
       <c r="B5" t="str">
-        <v>学业功能下降</v>
+        <v>课堂纪律型</v>
       </c>
       <c r="C5" t="str">
         <v>student_case</v>
@@ -602,66 +579,386 @@
         <v>1</v>
       </c>
       <c r="E5" t="str">
-        <v>student_case,academic</v>
+        <v>行为,student_case</v>
       </c>
       <c r="F5" t="str">
-        <v>学业表现持续下降，且已有常规支持措施没有带来改善。</v>
+        <v>课堂讲话、随意走动、不遵守课堂基本规则</v>
       </c>
       <c r="G5" t="str">
-        <v>成绩持续下滑；作业和听课明显受影响</v>
+        <v>每天被点名提醒2次及以上</v>
       </c>
       <c r="H5" t="str">
-        <v>可能是学习问题模块的信号，需要交叉评估</v>
+        <v>混乱型依恋学生的课堂纪律问题最难用常规行为管理解决——他们不是在挑战规则，是内部没有秩序感</v>
       </c>
       <c r="I5" t="str">
-        <v>转入学习问题模块做三层诊断，区分行为、认知与关系层面的卡点</v>
+        <v>用 T4 三步行为契约（可叠加 T2 信号约定与关系性肯定）</v>
       </c>
       <c r="J5" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SC_AT_05</v>
+        <v>B2</v>
       </c>
       <c r="B6" t="str">
-        <v>适应障碍信号</v>
+        <v>规则习惯型</v>
       </c>
       <c r="C6" t="str">
         <v>student_case</v>
       </c>
       <c r="D6" t="str">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E6" t="str">
-        <v>student_case,adapt,crisis</v>
+        <v>行为,student_case</v>
       </c>
       <c r="F6" t="str">
-        <v>出现拒学、躯体化或明显回避，且持续四周以上没有改善趋势。</v>
+        <v>不按时完成任务、撒谎、物品整理混乱</v>
       </c>
       <c r="G6" t="str">
-        <v>拒学、躯体不适、明显回避；持续四周以上</v>
+        <v>作业长期不交或敷衍，物品经常丢失</v>
       </c>
       <c r="H6" t="str">
-        <v>重大生活事件或长期压力累积</v>
+        <v>回避型依恋在规则面前的典型防御：规则=控制，「遵守规则=被控制=不安全」</v>
       </c>
       <c r="I6" t="str">
-        <v>整理时间线与已尝试措施，启动专业会商流程</v>
+        <v>用 T4 三步行为契约（量化版：从「一课桌」整理开始）</v>
       </c>
       <c r="J6" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>B3</v>
+      </c>
+      <c r="B7" t="str">
+        <v>攻击冲动型</v>
+      </c>
+      <c r="C7" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="D7" t="str">
+        <v>1.3</v>
+      </c>
+      <c r="E7" t="str">
+        <v>行为,student_case</v>
+      </c>
+      <c r="F7" t="str">
+        <v>攻击性语言、肢体冲突、破坏物品</v>
+      </c>
+      <c r="G7" t="str">
+        <v>一周内发生1次以上肢体冲突</v>
+      </c>
+      <c r="H7" t="str">
+        <v>混乱型依恋的核心行为表现。攻击不是目的而是求救——对安全连接的极度渴望以扭曲方式表达</v>
+      </c>
+      <c r="I7" t="str">
+        <v>用 T4 三步行为契约（增加关系目标）+ T12 心智化回应（不撑不退）</v>
+      </c>
+      <c r="J7" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>C1</v>
+      </c>
+      <c r="B8" t="str">
+        <v>焦虑退缩型</v>
+      </c>
+      <c r="C8" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="D8" t="str">
+        <v>1</v>
+      </c>
+      <c r="E8" t="str">
+        <v>情绪,student_case</v>
+      </c>
+      <c r="F8" t="str">
+        <v>过度紧张、回避挑战、恐惧社交。常伴有躯体症状</v>
+      </c>
+      <c r="G8" t="str">
+        <v>从不主动举手发言，回避社交场合</v>
+      </c>
+      <c r="H8" t="str">
+        <v>焦虑型依恋的核心表现。过度寻求安全信号却始终得不到满足→退缩</v>
+      </c>
+      <c r="I8" t="str">
+        <v>用 T3 渐进参与计划（安全基地启动优先），辅以 T8 优势发现日记</v>
+      </c>
+      <c r="J8" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>C2</v>
+      </c>
+      <c r="B9" t="str">
+        <v>情绪调节型</v>
+      </c>
+      <c r="C9" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="D9" t="str">
+        <v>1.3</v>
+      </c>
+      <c r="E9" t="str">
+        <v>情绪,student_case</v>
+      </c>
+      <c r="F9" t="str">
+        <v>情绪波动剧烈，与情境不成比例的愤怒/哭泣反应。可能与养育中的情绪忽视有关</v>
+      </c>
+      <c r="G9" t="str">
+        <v>情绪反应与情境不成比例；突然暴躁或崩溃</v>
+      </c>
+      <c r="H9" t="str">
+        <v>混乱型依恋的核心情绪表现形式。学生大脑的情绪警报系统长期处于高唤醒状态</v>
+      </c>
+      <c r="I9" t="str">
+        <v>用 T7 情绪命名与接纳 + T12 心智化回应（完整版），先稳定再上技术</v>
+      </c>
+      <c r="J9" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>C3</v>
+      </c>
+      <c r="B10" t="str">
+        <v>低自尊型</v>
+      </c>
+      <c r="C10" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="D10" t="str">
+        <v>1.3</v>
+      </c>
+      <c r="E10" t="str">
+        <v>情绪,student_case</v>
+      </c>
+      <c r="F10" t="str">
+        <v>认为自己不配被爱、不值得成功、做什么都不行</v>
+      </c>
+      <c r="G10" t="str">
+        <v>常说「我不行」「我太笨了」</v>
+      </c>
+      <c r="H10" t="str">
+        <v>所有不安全依恋类型的共同核心。被反复拒绝/忽视的体验内化→「我不值得」的内部工作模型</v>
+      </c>
+      <c r="I10" t="str">
+        <v>用 T8 优势发现日记（关系预热+具体到粒度的看见）+ T11 优势锚定法</v>
+      </c>
+      <c r="J10" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>D1</v>
+      </c>
+      <c r="B11" t="str">
+        <v>同伴冲突型</v>
+      </c>
+      <c r="C11" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="D11" t="str">
+        <v>1</v>
+      </c>
+      <c r="E11" t="str">
+        <v>社交,student_case</v>
+      </c>
+      <c r="F11" t="str">
+        <v>经常与同伴争吵、抢夺、被排斥或参与排挤他人</v>
+      </c>
+      <c r="G11" t="str">
+        <v>经常与同学冲突或起争执</v>
+      </c>
+      <c r="H11" t="str">
+        <v>混乱型依恋的社交表现。对他人的意图高度警惕（过度归因敌意），因为从未体验过可预测的安全关系</v>
+      </c>
+      <c r="I11" t="str">
+        <v>用 T12 心智化回应（冲突调解三步），辅以 T4 行为契约（社交版）</v>
+      </c>
+      <c r="J11" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>D2</v>
+      </c>
+      <c r="B12" t="str">
+        <v>社交退缩型</v>
+      </c>
+      <c r="C12" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="D12" t="str">
+        <v>1</v>
+      </c>
+      <c r="E12" t="str">
+        <v>社交,student_case</v>
+      </c>
+      <c r="F12" t="str">
+        <v>自由活动时间独自一人，不主动接近同伴，但不排斥他人</v>
+      </c>
+      <c r="G12" t="str">
+        <v>自由活动时间通常独自一人</v>
+      </c>
+      <c r="H12" t="str">
+        <v>回避型依恋的社交策略：「与其被拒绝，不如不参与」。自我保护的选择而非能力缺陷</v>
+      </c>
+      <c r="I12" t="str">
+        <v>用 T10 友谊桥同伴配对（告知同伴角色重要性），辅以 T9 社交剧本练习</v>
+      </c>
+      <c r="J12" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>D3</v>
+      </c>
+      <c r="B13" t="str">
+        <v>技能缺失型</v>
+      </c>
+      <c r="C13" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="D13" t="str">
+        <v>1</v>
+      </c>
+      <c r="E13" t="str">
+        <v>社交,student_case</v>
+      </c>
+      <c r="F13" t="str">
+        <v>不会用恰当方式加入游戏或对话。愿意交朋友但不知道方法</v>
+      </c>
+      <c r="G13" t="str">
+        <v>不会用恰当方式加入同伴游戏</v>
+      </c>
+      <c r="H13" t="str">
+        <v>不同于社交退缩——D3 是能力问题而非动机问题。安全型依恋也可能出现 D3</v>
+      </c>
+      <c r="I13" t="str">
+        <v>用 T9 社交剧本练习（安全基地预热），辅以 T10 友谊桥提供实践场</v>
+      </c>
+      <c r="J13" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>E1</v>
+      </c>
+      <c r="B14" t="str">
+        <v>亲子紧张型</v>
+      </c>
+      <c r="C14" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="D14" t="str">
+        <v>1.3</v>
+      </c>
+      <c r="E14" t="str">
+        <v>家庭,student_case</v>
+      </c>
+      <c r="F14" t="str">
+        <v>亲子沟通障碍、频繁冲突，家长教育方式不一致</v>
+      </c>
+      <c r="G14" t="str">
+        <v>亲子沟通存在明显障碍</v>
+      </c>
+      <c r="H14" t="str">
+        <v>不安全依恋的直接体现。家庭中的冲突模式被带入学校——学生对待老师的方式往往是家庭互动的镜像</v>
+      </c>
+      <c r="I14" t="str">
+        <v>用家校沟通指南（合作邀请模式+心智化话术·家长版），高年段可让学生参与三方沟通</v>
+      </c>
+      <c r="J14" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>E2</v>
+      </c>
+      <c r="B15" t="str">
+        <v>教养不当型</v>
+      </c>
+      <c r="C15" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2</v>
+      </c>
+      <c r="E15" t="str">
+        <v>家庭,安全,student_case</v>
+      </c>
+      <c r="F15" t="str">
+        <v>体罚、言语羞辱、忽视或过度控制。最高安全风险编码</v>
+      </c>
+      <c r="G15" t="str">
+        <v>存在体罚、暴力或忽视迹象；安全维度≥4</v>
+      </c>
+      <c r="H15" t="str">
+        <v>直接对应混乱型依恋的成因。E2 学生大脑中的「安全系统」从未被正常激活过，最高响应级别</v>
+      </c>
+      <c r="I15" t="str">
+        <v>立即启动学校安全流程：通知年级组长+德育处，暂停学业干预，启动专业转介机制</v>
+      </c>
+      <c r="J15" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>E3</v>
+      </c>
+      <c r="B16" t="str">
+        <v>支持缺位型</v>
+      </c>
+      <c r="C16" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="D16" t="str">
+        <v>1.3</v>
+      </c>
+      <c r="E16" t="str">
+        <v>家庭,student_case</v>
+      </c>
+      <c r="F16" t="str">
+        <v>家庭对学生的学业、情感支持明显缺失。如留守儿童/单亲家长无力兼顾</v>
+      </c>
+      <c r="G16" t="str">
+        <v>家庭支持明显缺位</v>
+      </c>
+      <c r="H16" t="str">
+        <v>回避型依恋的常见环境成因：「求助也没用」→学会不求助→变成独立但不连接的回避策略</v>
+      </c>
+      <c r="I16" t="str">
+        <v>用 T11 优势锚定法（独立·S0 发展）以学校为安全基地，替代部分家庭功能</v>
+      </c>
+      <c r="J16" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J16"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -691,22 +988,22 @@
         <v>SC_EV_01</v>
       </c>
       <c r="B2" t="str">
-        <v>SC_AT_01</v>
+        <v>A1</v>
       </c>
       <c r="C2" t="str">
         <v>SC_S1</v>
       </c>
       <c r="D2" t="str">
-        <v>维度[SC_S1D3] &gt;= 4</v>
+        <v>题[q3] &gt;= 3 或 题[q4] &gt;= 3 或 题[q5] &gt;= 3 或 题[q6] &gt;= 3 或 题[q8] &gt;= 3</v>
       </c>
       <c r="E2" t="str">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F2" t="str">
-        <v>情绪维度处于高位，已影响日常功能</v>
+        <v>注意力维持困难信号：走神/作业拖拉/需反复催促/物品混乱（关联信号，权重 3 归一 1.5）</v>
       </c>
       <c r="G2" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="3">
@@ -714,22 +1011,22 @@
         <v>SC_EV_02</v>
       </c>
       <c r="B3" t="str">
-        <v>SC_AT_01</v>
+        <v>A2</v>
       </c>
       <c r="C3" t="str">
         <v>SC_S1</v>
       </c>
       <c r="D3" t="str">
-        <v>维度[SC_S1D3] &gt;= 3</v>
+        <v>题[q5] &gt;= 3</v>
       </c>
       <c r="E3" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v>情绪维度出现需要关注的信号</v>
+        <v>需反复催促才开始学习任务（核心信号，权重 5 归一 2）</v>
       </c>
       <c r="G3" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="4">
@@ -737,22 +1034,22 @@
         <v>SC_EV_03</v>
       </c>
       <c r="B4" t="str">
-        <v>SC_AT_02</v>
+        <v>A2</v>
       </c>
       <c r="C4" t="str">
         <v>SC_S1</v>
       </c>
       <c r="D4" t="str">
-        <v>维度[SC_S1D2] &gt;= 4</v>
+        <v>题[q4] &gt;= 3</v>
       </c>
       <c r="E4" t="str">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F4" t="str">
-        <v>行为维度处于高位，行为频繁且难以预测</v>
+        <v>作业不交或敷衍（关联信号，权重 3 归一 1.5）</v>
       </c>
       <c r="G4" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="5">
@@ -760,22 +1057,22 @@
         <v>SC_EV_04</v>
       </c>
       <c r="B5" t="str">
-        <v>SC_AT_02</v>
+        <v>A3</v>
       </c>
       <c r="C5" t="str">
         <v>SC_S1</v>
       </c>
       <c r="D5" t="str">
-        <v>维度[SC_S1D2] &gt;= 3</v>
+        <v>题[q3] &gt;= 3</v>
       </c>
       <c r="E5" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="str">
-        <v>行为维度出现需要关注的信号</v>
+        <v>科目持续低于 75 分（核心信号，权重 5 归一 2）</v>
       </c>
       <c r="G5" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="6">
@@ -783,22 +1080,22 @@
         <v>SC_EV_05</v>
       </c>
       <c r="B6" t="str">
-        <v>SC_AT_03</v>
+        <v>B1</v>
       </c>
       <c r="C6" t="str">
         <v>SC_S1</v>
       </c>
       <c r="D6" t="str">
-        <v>维度[SC_S1D4] &gt;= 4</v>
+        <v>题[q6] &gt;= 3</v>
       </c>
       <c r="E6" t="str">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F6" t="str">
-        <v>同伴社交维度处于高位，冲突或孤立反复发生</v>
+        <v>每天被点名提醒 2 次及以上（核心信号，权重 5 归一 2）</v>
       </c>
       <c r="G6" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="7">
@@ -806,22 +1103,22 @@
         <v>SC_EV_06</v>
       </c>
       <c r="B7" t="str">
-        <v>SC_AT_03</v>
+        <v>B2</v>
       </c>
       <c r="C7" t="str">
         <v>SC_S1</v>
       </c>
       <c r="D7" t="str">
-        <v>维度[SC_S1D4] &gt;= 3</v>
+        <v>题[q4] &gt;= 3 或 题[q8] &gt;= 3</v>
       </c>
       <c r="E7" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>同伴社交出现需要关注的信号</v>
+        <v>作业长期不交或敷衍、物品整理混乱（核心信号，权重 5 归一 2）</v>
       </c>
       <c r="G7" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="8">
@@ -829,22 +1126,22 @@
         <v>SC_EV_07</v>
       </c>
       <c r="B8" t="str">
-        <v>SC_AT_04</v>
+        <v>B3</v>
       </c>
       <c r="C8" t="str">
         <v>SC_S1</v>
       </c>
       <c r="D8" t="str">
-        <v>维度[SC_S1D1] &gt;= 4</v>
+        <v>题[q7] &gt;= 3</v>
       </c>
       <c r="E8" t="str">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F8" t="str">
-        <v>学业维度处于高位且常规支持无效</v>
+        <v>一周内发生肢体冲突（核心信号，权重 5 归一 2）</v>
       </c>
       <c r="G8" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="9">
@@ -852,22 +1149,22 @@
         <v>SC_EV_08</v>
       </c>
       <c r="B9" t="str">
-        <v>SC_AT_04</v>
+        <v>B3</v>
       </c>
       <c r="C9" t="str">
         <v>SC_S1</v>
       </c>
       <c r="D9" t="str">
-        <v>维度[SC_S1D1] &gt;= 3</v>
+        <v>题[q10] &gt;= 3</v>
       </c>
       <c r="E9" t="str">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F9" t="str">
-        <v>学业表现出现下降</v>
+        <v>与情境不成比例的强烈情绪（关联信号，权重 3 归一 1.5）</v>
       </c>
       <c r="G9" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="10">
@@ -875,22 +1172,22 @@
         <v>SC_EV_09</v>
       </c>
       <c r="B10" t="str">
-        <v>SC_AT_05</v>
+        <v>C1</v>
       </c>
       <c r="C10" t="str">
         <v>SC_S1</v>
       </c>
       <c r="D10" t="str">
-        <v>维度[SC_S1D5] &gt;= 4</v>
+        <v>题[q9] &gt;= 3</v>
       </c>
       <c r="E10" t="str">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="F10" t="str">
-        <v>适应维度处于高位，出现拒学或躯体化信号</v>
+        <v>从不或极少主动举手发言（核心信号，权重 5 归一 2）</v>
       </c>
       <c r="G10" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="11">
@@ -898,22 +1195,22 @@
         <v>SC_EV_10</v>
       </c>
       <c r="B11" t="str">
-        <v>SC_AT_05</v>
+        <v>C1</v>
       </c>
       <c r="C11" t="str">
         <v>SC_S1</v>
       </c>
       <c r="D11" t="str">
-        <v>题[q15] &gt;= 4</v>
+        <v>题[q2] &gt;= 3 或 题[q11] &gt;= 3 或 题[q12] &gt;= 3</v>
       </c>
       <c r="E11" t="str">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F11" t="str">
-        <v>问题已持续四周以上且无改善趋势</v>
+        <v>被排斥/自我否定/独处等退缩信号（关联信号，权重 3 归一 1.5）</v>
       </c>
       <c r="G11" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="12">
@@ -921,22 +1218,22 @@
         <v>SC_EV_11</v>
       </c>
       <c r="B12" t="str">
-        <v>SC_AT_05</v>
+        <v>C2</v>
       </c>
       <c r="C12" t="str">
         <v>SC_S1</v>
       </c>
       <c r="D12" t="str">
-        <v>维度[SC_S1D5] &gt;= 3</v>
+        <v>题[q10] &gt;= 3</v>
       </c>
       <c r="E12" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="str">
-        <v>适应状况出现需要关注的信号</v>
+        <v>与情境不成比例的强烈情绪（核心信号，权重 5 归一 2）</v>
       </c>
       <c r="G12" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="13">
@@ -944,22 +1241,22 @@
         <v>SC_EV_12</v>
       </c>
       <c r="B13" t="str">
-        <v>SC_AT_02</v>
+        <v>C2</v>
       </c>
       <c r="C13" t="str">
-        <v>SC_S2</v>
+        <v>SC_S1</v>
       </c>
       <c r="D13" t="str">
-        <v>维度[SC_S2D1] &gt;= 3.5</v>
+        <v>题[q14] &gt;= 3</v>
       </c>
       <c r="E13" t="str">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F13" t="str">
-        <v>结构化观察显示行为诱因不清晰，难以预防</v>
+        <v>亲子沟通明显障碍（关联信号，权重 3 归一 1.5）</v>
       </c>
       <c r="G13" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="14">
@@ -967,22 +1264,22 @@
         <v>SC_EV_13</v>
       </c>
       <c r="B14" t="str">
-        <v>SC_AT_05</v>
+        <v>C3</v>
       </c>
       <c r="C14" t="str">
-        <v>SC_S2</v>
+        <v>SC_S1</v>
       </c>
       <c r="D14" t="str">
-        <v>维度[SC_S2D2] &gt;= 3.5</v>
+        <v>题[q11] &gt;= 3</v>
       </c>
       <c r="E14" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" t="str">
-        <v>结构化观察显示功能影响已经明显</v>
+        <v>常说「我不行」「我太笨了」（核心信号，权重 5 归一 2）</v>
       </c>
       <c r="G14" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="15">
@@ -990,22 +1287,22 @@
         <v>SC_EV_14</v>
       </c>
       <c r="B15" t="str">
-        <v>SC_AT_01</v>
+        <v>C3</v>
       </c>
       <c r="C15" t="str">
-        <v>SC_S2</v>
+        <v>SC_S1</v>
       </c>
       <c r="D15" t="str">
-        <v>维度[SC_S2D3] &gt;= 3.5</v>
+        <v>题[q9] &gt;= 3</v>
       </c>
       <c r="E15" t="str">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F15" t="str">
-        <v>已尝试的支持措施基本无效，需要升级支持层级</v>
+        <v>从不或极少主动举手发言（关联信号，权重 3 归一 1.5）</v>
       </c>
       <c r="G15" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="16">
@@ -1013,34 +1310,241 @@
         <v>SC_EV_15</v>
       </c>
       <c r="B16" t="str">
-        <v>SC_AT_03</v>
+        <v>D1</v>
       </c>
       <c r="C16" t="str">
-        <v>SC_S2</v>
+        <v>SC_S1</v>
       </c>
       <c r="D16" t="str">
-        <v>维度[SC_S2D2] &gt;= 3</v>
+        <v>题[q2] &gt;= 3</v>
       </c>
       <c r="E16" t="str">
+        <v>2</v>
+      </c>
+      <c r="F16" t="str">
+        <v>被欺凌或明显排斥（核心信号，权重 5 归一 2）</v>
+      </c>
+      <c r="G16" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>SC_EV_16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>D1</v>
+      </c>
+      <c r="C17" t="str">
+        <v>SC_S1</v>
+      </c>
+      <c r="D17" t="str">
+        <v>题[q7] &gt;= 3</v>
+      </c>
+      <c r="E17" t="str">
         <v>1.5</v>
       </c>
-      <c r="F16" t="str">
-        <v>功能影响已波及正常互动</v>
-      </c>
-      <c r="G16" t="str">
-        <v>学生个体问题手册v1</v>
+      <c r="F17" t="str">
+        <v>一周内发生肢体冲突（关联信号，权重 3 归一 1.5）</v>
+      </c>
+      <c r="G17" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SC_EV_17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>D2</v>
+      </c>
+      <c r="C18" t="str">
+        <v>SC_S1</v>
+      </c>
+      <c r="D18" t="str">
+        <v>题[q12] &gt;= 3</v>
+      </c>
+      <c r="E18" t="str">
+        <v>2</v>
+      </c>
+      <c r="F18" t="str">
+        <v>自由活动时间通常独自一人（核心信号，权重 5 归一 2）</v>
+      </c>
+      <c r="G18" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SC_EV_18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>D2</v>
+      </c>
+      <c r="C19" t="str">
+        <v>SC_S1</v>
+      </c>
+      <c r="D19" t="str">
+        <v>题[q13] &gt;= 3</v>
+      </c>
+      <c r="E19" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F19" t="str">
+        <v>不会用恰当方式加入同伴游戏（关联信号，权重 3 归一 1.5）</v>
+      </c>
+      <c r="G19" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SC_EV_19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>D3</v>
+      </c>
+      <c r="C20" t="str">
+        <v>SC_S1</v>
+      </c>
+      <c r="D20" t="str">
+        <v>题[q13] &gt;= 3</v>
+      </c>
+      <c r="E20" t="str">
+        <v>2</v>
+      </c>
+      <c r="F20" t="str">
+        <v>不会用恰当方式加入同伴游戏（核心信号，权重 5 归一 2）</v>
+      </c>
+      <c r="G20" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SC_EV_20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>E1</v>
+      </c>
+      <c r="C21" t="str">
+        <v>SC_S1</v>
+      </c>
+      <c r="D21" t="str">
+        <v>题[q14] &gt;= 3</v>
+      </c>
+      <c r="E21" t="str">
+        <v>2</v>
+      </c>
+      <c r="F21" t="str">
+        <v>亲子沟通存在明显障碍（核心信号，权重 5 归一 2）</v>
+      </c>
+      <c r="G21" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SC_EV_21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>E2</v>
+      </c>
+      <c r="C22" t="str">
+        <v>SC_S1</v>
+      </c>
+      <c r="D22" t="str">
+        <v>题[q1] &gt;= 3</v>
+      </c>
+      <c r="E22" t="str">
+        <v>2</v>
+      </c>
+      <c r="F22" t="str">
+        <v>存在体罚、暴力或忽视迹象（核心信号，权重 5 归一 2）</v>
+      </c>
+      <c r="G22" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>SC_EV_22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>E2</v>
+      </c>
+      <c r="C23" t="str">
+        <v>SC_S1</v>
+      </c>
+      <c r="D23" t="str">
+        <v>题[q15] &gt;= 3</v>
+      </c>
+      <c r="E23" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F23" t="str">
+        <v>家庭支持明显缺位（关联信号，权重 3 归一 1.5）</v>
+      </c>
+      <c r="G23" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SC_EV_23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>E3</v>
+      </c>
+      <c r="C24" t="str">
+        <v>SC_S1</v>
+      </c>
+      <c r="D24" t="str">
+        <v>题[q15] &gt;= 3</v>
+      </c>
+      <c r="E24" t="str">
+        <v>2</v>
+      </c>
+      <c r="F24" t="str">
+        <v>家庭支持明显缺位（核心信号，权重 5 归一 2）</v>
+      </c>
+      <c r="G24" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>SC_EV_24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>E3</v>
+      </c>
+      <c r="C25" t="str">
+        <v>SC_S1</v>
+      </c>
+      <c r="D25" t="str">
+        <v>题[q1] &gt;= 3</v>
+      </c>
+      <c r="E25" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="F25" t="str">
+        <v>存在体罚、暴力或忽视迹象（关联信号，权重 3 归一 1.5）</v>
+      </c>
+      <c r="G25" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G25"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1106,13 +1610,13 @@
         <v>10</v>
       </c>
       <c r="E2" t="str">
-        <v>总分 &gt;= 52</v>
+        <v>题[q1] &gt;= 4 或 题[q2] &gt;= 4</v>
       </c>
       <c r="F2" t="str">
         <v>red</v>
       </c>
       <c r="G2" t="str">
-        <v>L3 专业会商</v>
+        <v>红色-紧急响应</v>
       </c>
       <c r="H2" t="str">
         <v>crisis</v>
@@ -1121,25 +1625,25 @@
         <v>是</v>
       </c>
       <c r="J2" t="str">
-        <v>多个维度同时处于高位，已达到专业会商层级，请整理材料并启动转介。</v>
+        <v>SAFETY 维度（题1/题2）≥4 分，触发安全红线，需 24 小时内完成安全评估与安全计划</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>安全风险未在 24 小时内解除，或出现自杀/自伤/严重攻击信号</v>
       </c>
       <c r="L2" t="str">
-        <v>心理专员</v>
+        <v>心理健康中心/危机小组（心理总监）</v>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>安全计划确认后按危机小组要求复查</v>
       </c>
       <c r="N2" t="str">
         <v/>
       </c>
       <c r="O2" t="str">
-        <v/>
+        <v>立即启动学校安全流程，通知年级组长+德育处；暂停常规评估与学业干预，优先安全；家校安全沟通，24小时内完成安全评估与安全计划</v>
       </c>
       <c r="P2" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="3">
@@ -1156,13 +1660,13 @@
         <v>20</v>
       </c>
       <c r="E3" t="str">
-        <v>总分 &gt;= 38</v>
+        <v>总分 &gt;= 45</v>
       </c>
       <c r="F3" t="str">
         <v>orange</v>
       </c>
       <c r="G3" t="str">
-        <v>L2 年级协同</v>
+        <v>橙色-高响应</v>
       </c>
       <c r="H3" t="str">
         <v>high</v>
@@ -1171,25 +1675,25 @@
         <v>否</v>
       </c>
       <c r="J3" t="str">
-        <v>问题已超出单个教师可独立处理的范围，建议启动年级协同。</v>
+        <v>≥3 个编码激活或六维 D/E≥3，进入 L3 中心会商</v>
       </c>
       <c r="K3" t="str">
-        <v>连续两次 L2</v>
+        <v>多维度持续加重无缓解，或功能严重受损超过 4 周</v>
       </c>
       <c r="L3" t="str">
-        <v>年级组长</v>
+        <v>心理教师主导的中心会商（校领导+年级组长+班主任）</v>
       </c>
       <c r="M3" t="str">
-        <v>14天后复评</v>
+        <v>每 2 周复评</v>
       </c>
       <c r="N3" t="str">
         <v/>
       </c>
       <c r="O3" t="str">
-        <v/>
+        <v>启动 S2 全方位评估（课堂观察/学生访谈/科任交叉/家长沟通/六维评估）；制定综合干预方案，纳入年级组周例会讨论</v>
       </c>
       <c r="P3" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="4">
@@ -1206,13 +1710,13 @@
         <v>30</v>
       </c>
       <c r="E4" t="str">
-        <v>总分 &gt;= 25</v>
+        <v>总分 &gt;= 30 且 题[q1] &lt;= 3 且 题[q2] &lt;= 3</v>
       </c>
       <c r="F4" t="str">
         <v>yellow</v>
       </c>
       <c r="G4" t="str">
-        <v>L1 教师关注</v>
+        <v>黄色-中响应</v>
       </c>
       <c r="H4" t="str">
         <v>medium</v>
@@ -1221,180 +1725,380 @@
         <v>否</v>
       </c>
       <c r="J4" t="str">
-        <v>总分处于关注区间，暂不需要年级协同</v>
+        <v>≥2 个编码激活（无安全信号），启动 L2 年级协同</v>
       </c>
       <c r="K4" t="str">
-        <v/>
+        <v>功能受损持续 2-4 周无缓解，或升级为≥3 个编码激活</v>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>年级组长</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>每 2 周复评</v>
       </c>
       <c r="N4" t="str">
         <v/>
       </c>
       <c r="O4" t="str">
-        <v/>
+        <v>启动 S2 分层评估（六维评估+优势测评）；制定组合干预方案，按双周记录进展</v>
       </c>
       <c r="P4" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SC_GR_AUTO_01</v>
+        <v>SC_GR_04</v>
       </c>
       <c r="B5" t="str">
         <v>student_case</v>
       </c>
       <c r="C5" t="str">
-        <v>SC_S2</v>
+        <v>SC_S1</v>
       </c>
       <c r="D5" t="str">
-        <v>501</v>
+        <v>40</v>
       </c>
       <c r="E5" t="str">
-        <v>均分 &gt;= 4</v>
+        <v>总分 &gt;= 18 且 题[q1] &lt;= 3 且 题[q2] &lt;= 3</v>
       </c>
       <c r="F5" t="str">
-        <v>orange</v>
+        <v>blue</v>
       </c>
       <c r="G5" t="str">
-        <v>L2 年级协同</v>
+        <v>蓝色-低风险</v>
       </c>
       <c r="H5" t="str">
-        <v>high</v>
+        <v>low</v>
       </c>
       <c r="I5" t="str">
         <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>问题已超出单个教师可独立处理的范围，建议启动年级协同。</v>
+        <v>单一信号或单一短板，L1 班级自主干预</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>单一信号持续 1 个月无改善，或转为多个编码激活</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>年级组长（升级 L2 年级协同）</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>每 2 周复评</v>
       </c>
       <c r="N5" t="str">
         <v/>
       </c>
       <c r="O5" t="str">
-        <v/>
+        <v>启动标准诊疗流程（S1→S2→S3→S4）；使用对应编码的干预技术，按月记录进展</v>
       </c>
       <c r="P5" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SC_GR_AUTO_02</v>
+        <v>SC_GR_05</v>
       </c>
       <c r="B6" t="str">
         <v>student_case</v>
       </c>
       <c r="C6" t="str">
-        <v>SC_S2</v>
+        <v>SC_S1</v>
       </c>
       <c r="D6" t="str">
-        <v>502</v>
+        <v>50</v>
       </c>
       <c r="E6" t="str">
-        <v>均分 &gt;= 3.5</v>
+        <v>总分 &lt;= 17</v>
       </c>
       <c r="F6" t="str">
-        <v>yellow</v>
+        <v>green</v>
       </c>
       <c r="G6" t="str">
-        <v>L1 教师关注</v>
+        <v>紫色-待观察</v>
       </c>
       <c r="H6" t="str">
-        <v>medium</v>
+        <v>low</v>
       </c>
       <c r="I6" t="str">
         <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>总分处于关注区间，暂不需要年级协同</v>
+        <v>无明确信号，纳入预防性关注台账与 S0 优势发展路径</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>后续筛查出现维度标记（≥3 个）或编码激活</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>S1→S2 分层评估</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>每学期复评</v>
       </c>
       <c r="N6" t="str">
-        <v/>
+        <v>SC_RX_16</v>
       </c>
       <c r="O6" t="str">
-        <v/>
+        <v>安排优势测评，制定优势发展目标（S0 优势发展路径）；纳入预防性关注台账，每学期末复查五维筛查</v>
       </c>
       <c r="P6" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SC_GR_DEFAULT</v>
+        <v>SC_GR_AUTO_01</v>
       </c>
       <c r="B7" t="str">
         <v>student_case</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>SC_S2</v>
       </c>
       <c r="D7" t="str">
-        <v>999</v>
+        <v>501</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>均分 &gt;= 4</v>
       </c>
       <c r="F7" t="str">
-        <v>green</v>
+        <v>orange</v>
       </c>
       <c r="G7" t="str">
-        <v>L1 教师支持</v>
+        <v>橙色-高响应</v>
       </c>
       <c r="H7" t="str">
-        <v>low</v>
+        <v>high</v>
       </c>
       <c r="I7" t="str">
         <v>否</v>
       </c>
       <c r="J7" t="str">
+        <v>≥3 个编码激活或六维 D/E≥3，进入 L3 中心会商</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>SC_GR_AUTO_02</v>
+      </c>
+      <c r="B8" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="C8" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="D8" t="str">
+        <v>502</v>
+      </c>
+      <c r="E8" t="str">
+        <v>均分 &gt;= 3.5</v>
+      </c>
+      <c r="F8" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="G8" t="str">
+        <v>黄色-中响应</v>
+      </c>
+      <c r="H8" t="str">
+        <v>medium</v>
+      </c>
+      <c r="I8" t="str">
+        <v>否</v>
+      </c>
+      <c r="J8" t="str">
+        <v>≥2 个编码激活（无安全信号），启动 L2 年级协同</v>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>SC_GR_AUTO_03</v>
+      </c>
+      <c r="B9" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="C9" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="D9" t="str">
+        <v>503</v>
+      </c>
+      <c r="E9" t="str">
+        <v>均分 &gt;= 3</v>
+      </c>
+      <c r="F9" t="str">
+        <v>blue</v>
+      </c>
+      <c r="G9" t="str">
+        <v>蓝色-低风险</v>
+      </c>
+      <c r="H9" t="str">
+        <v>low</v>
+      </c>
+      <c r="I9" t="str">
+        <v>否</v>
+      </c>
+      <c r="J9" t="str">
+        <v>单一信号或单一短板，L1 班级自主干预</v>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SC_GR_AUTO_04</v>
+      </c>
+      <c r="B10" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="C10" t="str">
+        <v>SC_S2</v>
+      </c>
+      <c r="D10" t="str">
+        <v>504</v>
+      </c>
+      <c r="E10" t="str">
+        <v>均分 &gt;= 3</v>
+      </c>
+      <c r="F10" t="str">
+        <v>green</v>
+      </c>
+      <c r="G10" t="str">
+        <v>紫色-待观察</v>
+      </c>
+      <c r="H10" t="str">
+        <v>low</v>
+      </c>
+      <c r="I10" t="str">
+        <v>否</v>
+      </c>
+      <c r="J10" t="str">
+        <v>无明确信号，纳入预防性关注台账与 S0 优势发展路径</v>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SC_GR_DEFAULT</v>
+      </c>
+      <c r="B11" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v>999</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>green</v>
+      </c>
+      <c r="G11" t="str">
+        <v>暂无明显信号</v>
+      </c>
+      <c r="H11" t="str">
+        <v>low</v>
+      </c>
+      <c r="I11" t="str">
+        <v>否</v>
+      </c>
+      <c r="J11" t="str">
         <v>本次评估未发现需要重点干预的信号</v>
       </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
-        <v/>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v>学生个体问题手册v1</v>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P11"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1440,31 +2144,31 @@
         <v>student_case</v>
       </c>
       <c r="B2" t="str">
-        <v>量表[SC_S1].总分 &gt;= 52</v>
+        <v>量表[SC_S1].题[q1] &gt;= 4 或 量表[SC_S1].题[q2] &gt;= 4</v>
       </c>
       <c r="C2" t="str">
-        <v>多个维度同时处于高位，已达到专业会商层级，请整理材料并启动转介。</v>
+        <v>SAFETY 维度（题1/题2）≥4 分，触发安全红线，需 24 小时内完成安全评估与安全计划</v>
       </c>
       <c r="D2" t="str">
         <v>module</v>
       </c>
       <c r="E2" t="str">
-        <v>立即阻断常规建议输出，展示危机求助指引，生成转介工单通知心理专员</v>
+        <v>暂停常规评估，立即启动学校安全流程，通知年级组长与德育处，24小时内完成安全评估与安全计划</v>
       </c>
       <c r="F2" t="str">
-        <v>停止常规建议输出；展示危机求助指引；创建安全事件；生成转介工单；通知心理专员</v>
+        <v>暂停常规评估，立即启动学校安全流程，通知年级组长与德育处，24小时内完成安全评估与安全计划，必要时转心理健康中心</v>
       </c>
       <c r="G2" t="str">
-        <v>心理专员完成评估并在系统中标记为「已处置」</v>
+        <v>心理健康中心/危机小组专业评估确认安全风险解除后，恢复常规评估与干预流程</v>
       </c>
       <c r="H2" t="str">
-        <v>心理专员</v>
+        <v>班主任（联动年级组长、德育处、心理健康中心）</v>
       </c>
       <c r="I2" t="str">
-        <v>[学生]个体问题评估触发红线：出现拒学与情绪功能受损。请尽快介入。</v>
+        <v>[学生个体问题·红色紧急响应] 学生触发安全红线：题1/题2（体罚暴力/被欺凌排斥）≥4 分。已暂停常规评估并启动学校安全流程，请年级组长与德育处 24 小时内介入，通知家长并完成安全评估。</v>
       </c>
       <c r="J2" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
     </row>
   </sheetData>
